--- a/leads.xlsx
+++ b/leads.xlsx
@@ -1,34 +1,52 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Leads" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
   <fonts count="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +65,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -199,6 +150,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -233,6 +185,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -267,20 +220,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -402,463 +351,452 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H23"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Company Name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Contact Person</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Demand</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Generated Subject</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Generated Email Body</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Sent Timestamp</t>
-        </is>
+      <c r="A1" t="str">
+        <v>Company Name</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Contact Person</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Email</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Demand</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Generated Subject</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Generated Email Body</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Sent Timestamp</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Nextzee</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Raghav Tiwari</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>rt191708@gmail.com</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>we need elixer for silo liquid nature</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Precise Liquid Level Solutions for Nextzee | SAPCON</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;!DOCTYPE html&gt;
-&lt;html lang="en"&gt;
-&lt;head&gt;
-&lt;meta charset="UTF-8"&gt;
-&lt;meta name="viewport" content="width=device-width, initial-scale=1.0"&gt;
-&lt;title&gt;SAPCON Instruments&lt;/title&gt;
-&lt;style type="text/css"&gt;
-  body {
-    margin: 0;
-    padding: 20px 0;
-    background-color: #f1f5f9;
-    font-family: Arial, Helvetica, sans-serif;
-    color: #2d3748;
-    -webkit-font-smoothing: antialiased;
-  }
-  .email-container {
-    max-width: 620px;
-    margin: 0 auto;
-    background-color: #ffffff;
-    border: 1px solid #e2e8f0;
-    border-radius: 8px;
-    overflow: hidden;
-    box-shadow: 0 4px 16px rgba(15, 44, 89, 0.08);
-  }
-  .email-body {
-    padding: 24pt 24pt 14pt 24pt;
-    font-size: 11pt;
-    line-height: 1.5;
-    color: #2d3748;
-  }
-  .email-body p {
-    margin: 0 0 10pt 0;
-  }
-  .signature-card {
-    background-color: #ffffff;
-    border-top: 1px solid #e2e8f0;
-    padding: 16pt 24pt;
-  }
-  .sig-table {
-    width: 100%;
-    border-collapse: collapse;
-  }
-  .sig-logo-td {
-    width: 95px;
-    vertical-align: middle;
-    padding-right: 16pt;
-    border-right: 1.5pt solid #0f2c59;
-  }
-  .sig-logo-td img {
-    width: 88px;
-    height: auto;
-    display: block;
-  }
-  .sig-info-td {
-    vertical-align: middle;
-    padding-left: 16pt;
-    font-size: 10pt;
-    line-height: 1.35;
-    color: #4a5568;
-  }
-  .sig-thanks {
-    font-size: 10.5pt;
-    color: #2d3748;
-    margin-bottom: 2px;
-  }
-  .sig-name {
-    font-size: 11pt;
-    font-weight: 700;
-    color: #0f2c59;
-  }
-  .sig-desig {
-    font-size: 9.5pt;
-    color: #4a5568;
-    margin-bottom: 3px;
-  }
-  .sig-company {
-    font-size: 10pt;
-    font-weight: 700;
-    color: #2d3748;
-  }
-  .sig-contact {
-    font-size: 9pt;
-    color: #4a5568;
-    margin-top: 3px;
-  }
-  .sig-link {
-    color: #0f2c59;
-    text-decoration: underline;
-    font-weight: 600;
-  }
-  .footer-bar {
-    background-color: #f8fafc;
-    border-top: 1px solid #e2e8f0;
-    padding: 14pt 24pt;
-    text-align: center;
-    font-size: 9.5pt;
-    color: #718096;
-    line-height: 1.4;
-  }
-&lt;/style&gt;
-&lt;/head&gt;
-&lt;body&gt;
-  &lt;div class="email-container"&gt;
-    &lt;div class="email-body"&gt;
-      &lt;p&gt;Dear Raghav Tiwari,&lt;/p&gt;
-      &lt;p&gt;Greetings from &lt;strong&gt;SAPCON Instruments Pvt. Ltd.&lt;/strong&gt;&lt;/p&gt;
-      &lt;p style="margin-top:12pt;"&gt;Please find attached our product details featuring the &lt;a href="https://www.sapconinstruments.com/products/vibrating-fork-level-switch-elixir" target="_blank" style="color:#0f2c59; font-weight:700; text-decoration:underline;"&gt;Vibrating Fork (Elixir)&lt;/a&gt; for Liquid Level Switching &amp; Tank Automation.&lt;/p&gt;
-      &lt;p style="margin:12pt 0; line-height:1.5; color:#2d3748;"&gt;At SAPCON Instruments, with over 40 years of engineering excellence and 90,000+ global installations, our 'Elixir' Vibrating Fork level switch provides reliable, maintenance-free high/low level switching for liquid storage silos. Backed by PESO certifications and robust industrial design, it ensures fail-safe operation for your specific liquid handling requirements.&lt;/p&gt;
-      &lt;p style="margin-top:12pt;"&gt;We would be pleased to support your project and regular instrumentation requirements and provide further technical or commercial details based on your application.&lt;/p&gt;
-      &lt;p style="margin-top:12pt; margin-bottom:0;"&gt;Looking forward to your requirements.&lt;/p&gt;
-    &lt;/div&gt;
-    &lt;div style="padding:4pt 24pt 16pt 24pt;"&gt;
-      &lt;div style="background-color:#f8fafc; border:1px solid #e2e8f0; border-left:4px solid #0f2c59; border-radius:6px; padding:12px 18px;"&gt;
-        &lt;span style="font-size:10pt; color:#4a5568;"&gt;Recommended Product:&lt;/span&gt;
-        &lt;strong style="font-size:11pt; color:#0f2c59; display:block; margin:2px 0 6px 0;"&gt;Vibrating Fork (Elixir)&lt;/strong&gt;
-        &lt;a href="https://www.sapconinstruments.com/products/vibrating-fork-level-switch-elixir" target="_blank" style="display:inline-block; font-size:9.5pt; font-weight:700; color:#0f2c59; text-decoration:underline;"&gt;
-          View Technical Specifications on SAPCON &amp;rarr;
-        &lt;/a&gt;
-      &lt;/div&gt;
-    &lt;/div&gt;
-    &lt;div class="signature-card"&gt;
-      &lt;table class="sig-table"&gt;
-        &lt;tr&gt;
-          &lt;td class="sig-logo-td"&gt;
-            &lt;img src="/images/image1.png" alt="SAPCON Instruments Official Logo"&gt;
-          &lt;/td&gt;
-          &lt;td class="sig-info-td"&gt;
-            &lt;div class="sig-thanks"&gt;Thanks &amp;amp; Regards,&lt;/div&gt;
-            &lt;div class="sig-name"&gt;Elvis Joseph&lt;/div&gt;
-            &lt;div class="sig-desig"&gt;Regional Manager – South India Sales&lt;/div&gt;
-            &lt;div class="sig-company"&gt;SAPCON Instruments Pvt. Ltd.&lt;/div&gt;
-            &lt;div class="sig-contact"&gt;
-              P: 8871428228 / 0731-4757576, 75&lt;br&gt;
-              W: &lt;a href="https://www.sapconinstruments.com" class="sig-link" target="_blank"&gt;sapconinstruments.com&lt;/a&gt;
-            &lt;/div&gt;
-          &lt;/td&gt;
-        &lt;/tr&gt;
-      &lt;/table&gt;
-    &lt;/div&gt;
-    &lt;div class="footer-bar"&gt;
-      &lt;div&gt;&amp;copy; 2026 SAPCON Instruments. All rights reserved.&lt;/div&gt;
-      &lt;div&gt;Process Control Instrumentation &amp;bull; Indore, India&lt;/div&gt;
-    &lt;/div&gt;
-  &lt;/div&gt;
-&lt;/body&gt;
-&lt;/html&gt;
-</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Sent</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>16-Oct-2026 11:31 AM</t>
-        </is>
+    <row r="2" xml:space="preserve">
+      <c r="A2" t="str">
+        <v>Nextzee</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Raghav Tiwari</v>
+      </c>
+      <c r="C2" t="str">
+        <v>rt191708@gmail.com</v>
+      </c>
+      <c r="D2" t="str">
+        <v>we need elixer for silo liquid nature</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Precise Liquid Level Solutions for Nextzee | SAPCON</v>
+      </c>
+      <c r="F2" t="str" xml:space="preserve">
+        <v xml:space="preserve">&lt;!DOCTYPE html&gt;_x000d_
+&lt;html lang="en"&gt;_x000d_
+&lt;head&gt;_x000d_
+&lt;meta charset="UTF-8"&gt;_x000d_
+&lt;meta name="viewport" content="width=device-width, initial-scale=1.0"&gt;_x000d_
+&lt;title&gt;SAPCON Instruments&lt;/title&gt;_x000d_
+&lt;style type="text/css"&gt;_x000d_
+  body {_x000d_
+    margin: 0;_x000d_
+    padding: 20px 0;_x000d_
+    background-color: #f1f5f9;_x000d_
+    font-family: Arial, Helvetica, sans-serif;_x000d_
+    color: #2d3748;_x000d_
+    -webkit-font-smoothing: antialiased;_x000d_
+  }_x000d_
+  .email-container {_x000d_
+    max-width: 620px;_x000d_
+    margin: 0 auto;_x000d_
+    background-color: #ffffff;_x000d_
+    border: 1px solid #e2e8f0;_x000d_
+    border-radius: 8px;_x000d_
+    overflow: hidden;_x000d_
+    box-shadow: 0 4px 16px rgba(15, 44, 89, 0.08);_x000d_
+  }_x000d_
+  .email-body {_x000d_
+    padding: 24pt 24pt 14pt 24pt;_x000d_
+    font-size: 11pt;_x000d_
+    line-height: 1.5;_x000d_
+    color: #2d3748;_x000d_
+  }_x000d_
+  .email-body p {_x000d_
+    margin: 0 0 10pt 0;_x000d_
+  }_x000d_
+  .signature-card {_x000d_
+    background-color: #ffffff;_x000d_
+    border-top: 1px solid #e2e8f0;_x000d_
+    padding: 16pt 24pt;_x000d_
+  }_x000d_
+  .sig-table {_x000d_
+    width: 100%;_x000d_
+    border-collapse: collapse;_x000d_
+  }_x000d_
+  .sig-logo-td {_x000d_
+    width: 95px;_x000d_
+    vertical-align: middle;_x000d_
+    padding-right: 16pt;_x000d_
+    border-right: 1.5pt solid #0f2c59;_x000d_
+  }_x000d_
+  .sig-logo-td img {_x000d_
+    width: 88px;_x000d_
+    height: auto;_x000d_
+    display: block;_x000d_
+  }_x000d_
+  .sig-info-td {_x000d_
+    vertical-align: middle;_x000d_
+    padding-left: 16pt;_x000d_
+    font-size: 10pt;_x000d_
+    line-height: 1.35;_x000d_
+    color: #4a5568;_x000d_
+  }_x000d_
+  .sig-thanks {_x000d_
+    font-size: 10.5pt;_x000d_
+    color: #2d3748;_x000d_
+    margin-bottom: 2px;_x000d_
+  }_x000d_
+  .sig-name {_x000d_
+    font-size: 11pt;_x000d_
+    font-weight: 700;_x000d_
+    color: #0f2c59;_x000d_
+  }_x000d_
+  .sig-desig {_x000d_
+    font-size: 9.5pt;_x000d_
+    color: #4a5568;_x000d_
+    margin-bottom: 3px;_x000d_
+  }_x000d_
+  .sig-company {_x000d_
+    font-size: 10pt;_x000d_
+    font-weight: 700;_x000d_
+    color: #2d3748;_x000d_
+  }_x000d_
+  .sig-contact {_x000d_
+    font-size: 9pt;_x000d_
+    color: #4a5568;_x000d_
+    margin-top: 3px;_x000d_
+  }_x000d_
+  .sig-link {_x000d_
+    color: #0f2c59;_x000d_
+    text-decoration: underline;_x000d_
+    font-weight: 600;_x000d_
+  }_x000d_
+  .footer-bar {_x000d_
+    background-color: #f8fafc;_x000d_
+    border-top: 1px solid #e2e8f0;_x000d_
+    padding: 14pt 24pt;_x000d_
+    text-align: center;_x000d_
+    font-size: 9.5pt;_x000d_
+    color: #718096;_x000d_
+    line-height: 1.4;_x000d_
+  }_x000d_
+&lt;/style&gt;_x000d_
+&lt;/head&gt;_x000d_
+&lt;body&gt;_x000d_
+  &lt;div class="email-container"&gt;_x000d_
+    &lt;div class="email-body"&gt;_x000d_
+      &lt;p&gt;Dear Raghav Tiwari,&lt;/p&gt;_x000d_
+      &lt;p&gt;Greetings from &lt;strong&gt;SAPCON Instruments Pvt. Ltd.&lt;/strong&gt;&lt;/p&gt;_x000d_
+      &lt;p style="margin-top:12pt;"&gt;Please find attached our product details featuring the &lt;a href="https://www.sapconinstruments.com/products/vibrating-fork-level-switch-elixir" target="_blank" style="color:#0f2c59; font-weight:700; text-decoration:underline;"&gt;Vibrating Fork (Elixir)&lt;/a&gt; for Liquid Level Switching &amp; Tank Automation.&lt;/p&gt;_x000d_
+      &lt;p style="margin:12pt 0; line-height:1.5; color:#2d3748;"&gt;At SAPCON Instruments, with over 40 years of engineering excellence and 90,000+ global installations, our 'Elixir' Vibrating Fork level switch provides reliable, maintenance-free high/low level switching for liquid storage silos. Backed by PESO certifications and robust industrial design, it ensures fail-safe operation for your specific liquid handling requirements.&lt;/p&gt;_x000d_
+      &lt;p style="margin-top:12pt;"&gt;We would be pleased to support your project and regular instrumentation requirements and provide further technical or commercial details based on your application.&lt;/p&gt;_x000d_
+      &lt;p style="margin-top:12pt; margin-bottom:0;"&gt;Looking forward to your requirements.&lt;/p&gt;_x000d_
+    &lt;/div&gt;_x000d_
+_x000d_
+    _x000d_
+    &lt;div style="padding:4pt 24pt 16pt 24pt;"&gt;_x000d_
+      &lt;div style="background-color:#f8fafc; border:1px solid #e2e8f0; border-left:4px solid #0f2c59; border-radius:6px; padding:12px 18px;"&gt;_x000d_
+        &lt;span style="font-size:10pt; color:#4a5568;"&gt;Recommended Product:&lt;/span&gt;_x000d_
+        &lt;strong style="font-size:11pt; color:#0f2c59; display:block; margin:2px 0 6px 0;"&gt;Vibrating Fork (Elixir)&lt;/strong&gt;_x000d_
+        &lt;a href="https://www.sapconinstruments.com/products/vibrating-fork-level-switch-elixir" target="_blank" style="display:inline-block; font-size:9.5pt; font-weight:700; color:#0f2c59; text-decoration:underline;"&gt;_x000d_
+          View Technical Specifications on SAPCON &amp;rarr;_x000d_
+        &lt;/a&gt;_x000d_
+      &lt;/div&gt;_x000d_
+    &lt;/div&gt;_x000d_
+_x000d_
+_x000d_
+    &lt;div class="signature-card"&gt;_x000d_
+      &lt;table class="sig-table"&gt;_x000d_
+        &lt;tr&gt;_x000d_
+          &lt;td class="sig-logo-td"&gt;_x000d_
+            &lt;img src="/images/image1.png" alt="SAPCON Instruments Official Logo"&gt;_x000d_
+          &lt;/td&gt;_x000d_
+          &lt;td class="sig-info-td"&gt;_x000d_
+            &lt;div class="sig-thanks"&gt;Thanks &amp;amp; Regards,&lt;/div&gt;_x000d_
+            &lt;div class="sig-name"&gt;Elvis Joseph&lt;/div&gt;_x000d_
+            &lt;div class="sig-desig"&gt;Regional Manager – South India Sales&lt;/div&gt;_x000d_
+            &lt;div class="sig-company"&gt;SAPCON Instruments Pvt. Ltd.&lt;/div&gt;_x000d_
+            &lt;div class="sig-contact"&gt;_x000d_
+              P: 8871428228 / 0731-4757576, 75&lt;br&gt;_x000d_
+              W: &lt;a href="https://www.sapconinstruments.com" class="sig-link" target="_blank"&gt;sapconinstruments.com&lt;/a&gt;_x000d_
+            &lt;/div&gt;_x000d_
+          &lt;/td&gt;_x000d_
+        &lt;/tr&gt;_x000d_
+      &lt;/table&gt;_x000d_
+    &lt;/div&gt;_x000d_
+_x000d_
+    &lt;div class="footer-bar"&gt;_x000d_
+      &lt;div&gt;&amp;copy; 2026 SAPCON Instruments. All rights reserved.&lt;/div&gt;_x000d_
+      &lt;div&gt;Process Control Instrumentation &amp;bull; Indore, India&lt;/div&gt;_x000d_
+    &lt;/div&gt;_x000d_
+  &lt;/div&gt;_x000d_
+&lt;/body&gt;_x000d_
+&lt;/html&gt;_x000d_
+</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="H2" t="str">
+        <v>16-Oct-2026 11:31 AM</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>IMA</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Rahaber Raza</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ramsharma9724@gmail.com</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>we need vital and elixer and RF admistance for my plant urgent basis</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Urgent Level Instrumentation Solutions for IMA | SAPCON</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;!DOCTYPE html&gt;
-&lt;html lang="en"&gt;
-&lt;head&gt;
-&lt;meta charset="UTF-8"&gt;
-&lt;meta name="viewport" content="width=device-width, initial-scale=1.0"&gt;
-&lt;title&gt;SAPCON Instruments&lt;/title&gt;
-&lt;style type="text/css"&gt;
-  body {
-    margin: 0;
-    padding: 20px 0;
-    background-color: #f1f5f9;
-    font-family: Arial, Helvetica, sans-serif;
-    color: #2d3748;
-    -webkit-font-smoothing: antialiased;
-  }
-  .email-container {
-    max-width: 620px;
-    margin: 0 auto;
-    background-color: #ffffff;
-    border: 1px solid #e2e8f0;
-    border-radius: 8px;
-    overflow: hidden;
-    box-shadow: 0 4px 16px rgba(15, 44, 89, 0.08);
-  }
-  .email-body {
-    padding: 24pt 24pt 14pt 24pt;
-    font-size: 11pt;
-    line-height: 1.5;
-    color: #2d3748;
-  }
-  .email-body p {
-    margin: 0 0 10pt 0;
-  }
-  .signature-card {
-    background-color: #ffffff;
-    border-top: 1px solid #e2e8f0;
-    padding: 16pt 24pt;
-  }
-  .sig-table {
-    width: 100%;
-    border-collapse: collapse;
-  }
-  .sig-logo-td {
-    width: 95px;
-    vertical-align: middle;
-    padding-right: 16pt;
-    border-right: 1.5pt solid #0f2c59;
-  }
-  .sig-logo-td img {
-    width: 88px;
-    height: auto;
-    display: block;
-  }
-  .sig-info-td {
-    vertical-align: middle;
-    padding-left: 16pt;
-    font-size: 10pt;
-    line-height: 1.35;
-    color: #4a5568;
-  }
-  .sig-thanks {
-    font-size: 10.5pt;
-    color: #2d3748;
-    margin-bottom: 2px;
-  }
-  .sig-name {
-    font-size: 11pt;
-    font-weight: 700;
-    color: #0f2c59;
-  }
-  .sig-desig {
-    font-size: 9.5pt;
-    color: #4a5568;
-    margin-bottom: 3px;
-  }
-  .sig-company {
-    font-size: 10pt;
-    font-weight: 700;
-    color: #2d3748;
-  }
-  .sig-contact {
-    font-size: 9pt;
-    color: #4a5568;
-    margin-top: 3px;
-  }
-  .sig-link {
-    color: #0f2c59;
-    text-decoration: underline;
-    font-weight: 600;
-  }
-  .footer-bar {
-    background-color: #f8fafc;
-    border-top: 1px solid #e2e8f0;
-    padding: 14pt 24pt;
-    text-align: center;
-    font-size: 9.5pt;
-    color: #718096;
-    line-height: 1.4;
-  }
-&lt;/style&gt;
-&lt;/head&gt;
-&lt;body&gt;
-  &lt;div class="email-container"&gt;
-    &lt;div class="email-body"&gt;
-      &lt;p&gt;Dear Mr. Rahaber Raza,&lt;/p&gt;
-      &lt;p&gt;Greetings from &lt;strong&gt;SAPCON Instruments Pvt. Ltd.&lt;/strong&gt;&lt;/p&gt;
-      &lt;p style="margin-top:12pt;"&gt;Please find attached our product details featuring the &lt;a href="https://www.sapconinstruments.com/products/rf-admittance-level-switch-sla" target="_blank" style="color:#0f2c59; font-weight:700; text-decoration:underline;"&gt;RF Admittance Level Switch &amp; Vibrating Fork (Elixir)&lt;/a&gt; for Heavy Industrial Coating &amp; Hazardous Liquid Level Switching.&lt;/p&gt;
-      &lt;p style="margin:12pt 0; line-height:1.5; color:#2d3748;"&gt;Understanding your urgent requirement for reliable level switches at IMA, our RF Admittance switches and Elixir vibrating forks ensure precise, maintenance-free detection even under heavy material coating and demanding plant conditions. With over 40 years of proven reliability across 90,000+ global installations, SAPCON is equipped to dispatch these critical instruments on an expedited basis to minimize any operational downtime.&lt;/p&gt;
-      &lt;p style="margin-top:12pt;"&gt;We would be pleased to support your project and regular instrumentation requirements and provide further technical or commercial details based on your application.&lt;/p&gt;
-      &lt;p style="margin-top:12pt; margin-bottom:0;"&gt;Looking forward to your requirements.&lt;/p&gt;
-    &lt;/div&gt;
-    &lt;div style="padding:4pt 24pt 16pt 24pt;"&gt;
-      &lt;div style="background-color:#f8fafc; border:1px solid #e2e8f0; border-left:4px solid #0f2c59; border-radius:6px; padding:12px 18px;"&gt;
-        &lt;span style="font-size:10pt; color:#4a5568;"&gt;Recommended Product:&lt;/span&gt;
-        &lt;strong style="font-size:11pt; color:#0f2c59; display:block; margin:2px 0 6px 0;"&gt;RF Admittance Level Switch &amp; Vibrating Fork (Elixir)&lt;/strong&gt;
-        &lt;a href="https://www.sapconinstruments.com/products/rf-admittance-level-switch-sla" target="_blank" style="display:inline-block; font-size:9.5pt; font-weight:700; color:#0f2c59; text-decoration:underline;"&gt;
-          View Technical Specifications on SAPCON &amp;rarr;
-        &lt;/a&gt;
-      &lt;/div&gt;
-    &lt;/div&gt;
-    &lt;div class="signature-card"&gt;
-      &lt;table class="sig-table"&gt;
-        &lt;tr&gt;
-          &lt;td class="sig-logo-td"&gt;
-            &lt;img src="/images/image1.png" alt="SAPCON Instruments Official Logo"&gt;
-          &lt;/td&gt;
-          &lt;td class="sig-info-td"&gt;
-            &lt;div class="sig-thanks"&gt;Thanks &amp;amp; Regards,&lt;/div&gt;
-            &lt;div class="sig-name"&gt;Elvis Joseph&lt;/div&gt;
-            &lt;div class="sig-desig"&gt;Regional Manager – South India Sales&lt;/div&gt;
-            &lt;div class="sig-company"&gt;SAPCON Instruments Pvt. Ltd.&lt;/div&gt;
-            &lt;div class="sig-contact"&gt;
-              P: 8871428228 / 0731-4757576, 75&lt;br&gt;
-              W: &lt;a href="https://www.sapconinstruments.com" class="sig-link" target="_blank"&gt;sapconinstruments.com&lt;/a&gt;
-            &lt;/div&gt;
-          &lt;/td&gt;
-        &lt;/tr&gt;
-      &lt;/table&gt;
-    &lt;/div&gt;
-    &lt;div class="footer-bar"&gt;
-      &lt;div&gt;&amp;copy; 2026 SAPCON Instruments. All rights reserved.&lt;/div&gt;
-      &lt;div&gt;Process Control Instrumentation &amp;bull; Indore, India&lt;/div&gt;
-    &lt;/div&gt;
-  &lt;/div&gt;
-&lt;/body&gt;
-&lt;/html&gt;
-</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Sent</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>16-Oct-2026 11:31 AM</t>
-        </is>
+    <row r="3" xml:space="preserve">
+      <c r="A3" t="str">
+        <v>IMA</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Rahaber Raza</v>
+      </c>
+      <c r="C3" t="str">
+        <v>ramsharma9724@gmail.com</v>
+      </c>
+      <c r="D3" t="str">
+        <v>we need vital and elixer and RF admistance for my plant urgent basis</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Urgent Level Instrumentation Solutions for IMA | SAPCON</v>
+      </c>
+      <c r="F3" t="str" xml:space="preserve">
+        <v xml:space="preserve">&lt;!DOCTYPE html&gt;_x000d_
+&lt;html lang="en"&gt;_x000d_
+&lt;head&gt;_x000d_
+&lt;meta charset="UTF-8"&gt;_x000d_
+&lt;meta name="viewport" content="width=device-width, initial-scale=1.0"&gt;_x000d_
+&lt;title&gt;SAPCON Instruments&lt;/title&gt;_x000d_
+&lt;style type="text/css"&gt;_x000d_
+  body {_x000d_
+    margin: 0;_x000d_
+    padding: 20px 0;_x000d_
+    background-color: #f1f5f9;_x000d_
+    font-family: Arial, Helvetica, sans-serif;_x000d_
+    color: #2d3748;_x000d_
+    -webkit-font-smoothing: antialiased;_x000d_
+  }_x000d_
+  .email-container {_x000d_
+    max-width: 620px;_x000d_
+    margin: 0 auto;_x000d_
+    background-color: #ffffff;_x000d_
+    border: 1px solid #e2e8f0;_x000d_
+    border-radius: 8px;_x000d_
+    overflow: hidden;_x000d_
+    box-shadow: 0 4px 16px rgba(15, 44, 89, 0.08);_x000d_
+  }_x000d_
+  .email-body {_x000d_
+    padding: 24pt 24pt 14pt 24pt;_x000d_
+    font-size: 11pt;_x000d_
+    line-height: 1.5;_x000d_
+    color: #2d3748;_x000d_
+  }_x000d_
+  .email-body p {_x000d_
+    margin: 0 0 10pt 0;_x000d_
+  }_x000d_
+  .signature-card {_x000d_
+    background-color: #ffffff;_x000d_
+    border-top: 1px solid #e2e8f0;_x000d_
+    padding: 16pt 24pt;_x000d_
+  }_x000d_
+  .sig-table {_x000d_
+    width: 100%;_x000d_
+    border-collapse: collapse;_x000d_
+  }_x000d_
+  .sig-logo-td {_x000d_
+    width: 95px;_x000d_
+    vertical-align: middle;_x000d_
+    padding-right: 16pt;_x000d_
+    border-right: 1.5pt solid #0f2c59;_x000d_
+  }_x000d_
+  .sig-logo-td img {_x000d_
+    width: 88px;_x000d_
+    height: auto;_x000d_
+    display: block;_x000d_
+  }_x000d_
+  .sig-info-td {_x000d_
+    vertical-align: middle;_x000d_
+    padding-left: 16pt;_x000d_
+    font-size: 10pt;_x000d_
+    line-height: 1.35;_x000d_
+    color: #4a5568;_x000d_
+  }_x000d_
+  .sig-thanks {_x000d_
+    font-size: 10.5pt;_x000d_
+    color: #2d3748;_x000d_
+    margin-bottom: 2px;_x000d_
+  }_x000d_
+  .sig-name {_x000d_
+    font-size: 11pt;_x000d_
+    font-weight: 700;_x000d_
+    color: #0f2c59;_x000d_
+  }_x000d_
+  .sig-desig {_x000d_
+    font-size: 9.5pt;_x000d_
+    color: #4a5568;_x000d_
+    margin-bottom: 3px;_x000d_
+  }_x000d_
+  .sig-company {_x000d_
+    font-size: 10pt;_x000d_
+    font-weight: 700;_x000d_
+    color: #2d3748;_x000d_
+  }_x000d_
+  .sig-contact {_x000d_
+    font-size: 9pt;_x000d_
+    color: #4a5568;_x000d_
+    margin-top: 3px;_x000d_
+  }_x000d_
+  .sig-link {_x000d_
+    color: #0f2c59;_x000d_
+    text-decoration: underline;_x000d_
+    font-weight: 600;_x000d_
+  }_x000d_
+  .footer-bar {_x000d_
+    background-color: #f8fafc;_x000d_
+    border-top: 1px solid #e2e8f0;_x000d_
+    padding: 14pt 24pt;_x000d_
+    text-align: center;_x000d_
+    font-size: 9.5pt;_x000d_
+    color: #718096;_x000d_
+    line-height: 1.4;_x000d_
+  }_x000d_
+&lt;/style&gt;_x000d_
+&lt;/head&gt;_x000d_
+&lt;body&gt;_x000d_
+  &lt;div class="email-container"&gt;_x000d_
+    &lt;div class="email-body"&gt;_x000d_
+      &lt;p&gt;Dear Mr. Rahaber Raza,&lt;/p&gt;_x000d_
+      &lt;p&gt;Greetings from &lt;strong&gt;SAPCON Instruments Pvt. Ltd.&lt;/strong&gt;&lt;/p&gt;_x000d_
+      &lt;p style="margin-top:12pt;"&gt;Please find attached our product details featuring the &lt;a href="https://www.sapconinstruments.com/products/rf-admittance-level-switch-sla" target="_blank" style="color:#0f2c59; font-weight:700; text-decoration:underline;"&gt;RF Admittance Level Switch &amp; Vibrating Fork (Elixir)&lt;/a&gt; for Heavy Industrial Coating &amp; Hazardous Liquid Level Switching.&lt;/p&gt;_x000d_
+      &lt;p style="margin:12pt 0; line-height:1.5; color:#2d3748;"&gt;Understanding your urgent requirement for reliable level switches at IMA, our RF Admittance switches and Elixir vibrating forks ensure precise, maintenance-free detection even under heavy material coating and demanding plant conditions. With over 40 years of proven reliability across 90,000+ global installations, SAPCON is equipped to dispatch these critical instruments on an expedited basis to minimize any operational downtime.&lt;/p&gt;_x000d_
+      &lt;p style="margin-top:12pt;"&gt;We would be pleased to support your project and regular instrumentation requirements and provide further technical or commercial details based on your application.&lt;/p&gt;_x000d_
+      &lt;p style="margin-top:12pt; margin-bottom:0;"&gt;Looking forward to your requirements.&lt;/p&gt;_x000d_
+    &lt;/div&gt;_x000d_
+_x000d_
+    _x000d_
+    &lt;div style="padding:4pt 24pt 16pt 24pt;"&gt;_x000d_
+      &lt;div style="background-color:#f8fafc; border:1px solid #e2e8f0; border-left:4px solid #0f2c59; border-radius:6px; padding:12px 18px;"&gt;_x000d_
+        &lt;span style="font-size:10pt; color:#4a5568;"&gt;Recommended Product:&lt;/span&gt;_x000d_
+        &lt;strong style="font-size:11pt; color:#0f2c59; display:block; margin:2px 0 6px 0;"&gt;RF Admittance Level Switch &amp; Vibrating Fork (Elixir)&lt;/strong&gt;_x000d_
+        &lt;a href="https://www.sapconinstruments.com/products/rf-admittance-level-switch-sla" target="_blank" style="display:inline-block; font-size:9.5pt; font-weight:700; color:#0f2c59; text-decoration:underline;"&gt;_x000d_
+          View Technical Specifications on SAPCON &amp;rarr;_x000d_
+        &lt;/a&gt;_x000d_
+      &lt;/div&gt;_x000d_
+    &lt;/div&gt;_x000d_
+_x000d_
+_x000d_
+    &lt;div class="signature-card"&gt;_x000d_
+      &lt;table class="sig-table"&gt;_x000d_
+        &lt;tr&gt;_x000d_
+          &lt;td class="sig-logo-td"&gt;_x000d_
+            &lt;img src="/images/image1.png" alt="SAPCON Instruments Official Logo"&gt;_x000d_
+          &lt;/td&gt;_x000d_
+          &lt;td class="sig-info-td"&gt;_x000d_
+            &lt;div class="sig-thanks"&gt;Thanks &amp;amp; Regards,&lt;/div&gt;_x000d_
+            &lt;div class="sig-name"&gt;Elvis Joseph&lt;/div&gt;_x000d_
+            &lt;div class="sig-desig"&gt;Regional Manager – South India Sales&lt;/div&gt;_x000d_
+            &lt;div class="sig-company"&gt;SAPCON Instruments Pvt. Ltd.&lt;/div&gt;_x000d_
+            &lt;div class="sig-contact"&gt;_x000d_
+              P: 8871428228 / 0731-4757576, 75&lt;br&gt;_x000d_
+              W: &lt;a href="https://www.sapconinstruments.com" class="sig-link" target="_blank"&gt;sapconinstruments.com&lt;/a&gt;_x000d_
+            &lt;/div&gt;_x000d_
+          &lt;/td&gt;_x000d_
+        &lt;/tr&gt;_x000d_
+      &lt;/table&gt;_x000d_
+    &lt;/div&gt;_x000d_
+_x000d_
+    &lt;div class="footer-bar"&gt;_x000d_
+      &lt;div&gt;&amp;copy; 2026 SAPCON Instruments. All rights reserved.&lt;/div&gt;_x000d_
+      &lt;div&gt;Process Control Instrumentation &amp;bull; Indore, India&lt;/div&gt;_x000d_
+    &lt;/div&gt;_x000d_
+  &lt;/div&gt;_x000d_
+&lt;/body&gt;_x000d_
+&lt;/html&gt;_x000d_
+</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="H3" t="str">
+        <v>16-Oct-2026 11:31 AM</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Test Direct Send Co</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>raghavtiwari972003@gmail.com</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Ultrasonic level transmitter for water tank</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Precise Level Measurement for Test Direct Send Co | SAPCON</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;!DOCTYPE html&gt;
+    <row r="4" xml:space="preserve">
+      <c r="A4" t="str">
+        <v>Test Direct Send Co</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v>raghavtiwari972003@gmail.com</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Ultrasonic level transmitter for water tank</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Precise Level Measurement for Test Direct Send Co | SAPCON</v>
+      </c>
+      <c r="F4" t="str" xml:space="preserve">
+        <v xml:space="preserve">&lt;!DOCTYPE html&gt;
 &lt;html lang="en"&gt;
 &lt;head&gt;
 &lt;meta charset="UTF-8"&gt;
@@ -1004,233 +942,206 @@
   &lt;/div&gt;
 &lt;/body&gt;
 &lt;/html&gt;
-</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Sent</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>16-Oct-2026 11:36 AM</t>
-        </is>
+</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="H4" t="str">
+        <v>16-Oct-2026 11:36 AM</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Nextzee</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Raghav Tiwari</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>rt191708@gmail.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>we need elixer for silo liquid nature</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Level measurement enquiry for Nextzee silos</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;!DOCTYPE html&gt;
-&lt;html lang="en"&gt;
-&lt;head&gt;
-&lt;meta charset="UTF-8"&gt;
-&lt;meta name="viewport" content="width=device-width, initial-scale=1.0"&gt;
-&lt;title&gt;SAPCON Instruments&lt;/title&gt;
-&lt;style type="text/css"&gt;
-  body {
-    margin: 0;
-    padding: 20px 0;
-    background-color: #f1f5f9;
-    font-family: Arial, Helvetica, sans-serif;
-    color: #2d3748;
-    -webkit-font-smoothing: antialiased;
-  }
-  .email-container {
-    max-width: 620px;
-    margin: 0 auto;
-    background-color: #ffffff;
-    border: 1px solid #e2e8f0;
-    border-radius: 8px;
-    overflow: hidden;
-    box-shadow: 0 4px 16px rgba(15, 44, 89, 0.08);
-  }
-  .email-body {
-    padding: 24pt 24pt 14pt 24pt;
-    font-size: 11pt;
-    line-height: 1.5;
-    color: #2d3748;
-  }
-  .email-body p {
-    margin: 0 0 10pt 0;
-  }
-  .signature-card {
-    background-color: #ffffff;
-    border-top: 1px solid #e2e8f0;
-    padding: 16pt 24pt;
-  }
-  .sig-table {
-    width: 100%;
-    border-collapse: collapse;
-  }
-  .sig-logo-td {
-    width: 95px;
-    vertical-align: middle;
-    padding-right: 16pt;
-    border-right: 1.5pt solid #0f2c59;
-  }
-  .sig-logo-td img {
-    width: 88px;
-    height: auto;
-    display: block;
-  }
-  .sig-info-td {
-    vertical-align: middle;
-    padding-left: 16pt;
-    font-size: 10pt;
-    line-height: 1.35;
-    color: #4a5568;
-  }
-  .sig-thanks {
-    font-size: 10.5pt;
-    color: #2d3748;
-    margin-bottom: 2px;
-  }
-  .sig-name {
-    font-size: 11pt;
-    font-weight: 700;
-    color: #0f2c59;
-  }
-  .sig-desig {
-    font-size: 9.5pt;
-    color: #4a5568;
-    margin-bottom: 3px;
-  }
-  .sig-company {
-    font-size: 10pt;
-    font-weight: 700;
-    color: #2d3748;
-  }
-  .sig-contact {
-    font-size: 9pt;
-    color: #4a5568;
-    margin-top: 3px;
-  }
-  .sig-link {
-    color: #0f2c59;
-    text-decoration: underline;
-    font-weight: 600;
-  }
-  .footer-bar {
-    background-color: #f8fafc;
-    border-top: 1px solid #e2e8f0;
-    padding: 14pt 24pt;
-    text-align: center;
-    font-size: 9.5pt;
-    color: #718096;
-    line-height: 1.4;
-  }
-&lt;/style&gt;
-&lt;/head&gt;
-&lt;body&gt;
-  &lt;div class="email-container"&gt;
-    &lt;div class="email-body"&gt;
-      &lt;p&gt;Dear Raghav Tiwari,&lt;/p&gt;
-      &lt;p&gt;Greetings from &lt;strong&gt;SAPCON Instruments Pvt. Ltd.&lt;/strong&gt;&lt;/p&gt;
-      &lt;p style="margin-top:12pt;"&gt;Please find attached our product details featuring the &lt;a href="https://www.sapconinstruments.com/products/vibrating-fork-level-switch-elixir" target="_blank" style="color:#0f2c59; font-weight:700; text-decoration:underline;"&gt;Vibrating Fork (Elixir)&lt;/a&gt; for Liquid level detection in industrial silos.&lt;/p&gt;
-      &lt;p style="margin:12pt 0; line-height:1.5; color:#2d3748;"&gt;Hi Raghav, I understand you are looking for a reliable level switch to handle liquid applications in your silos. Our Elixir vibrating fork is ideally suited for this, offering dependable, no-moving-parts operation that resists buildup and integrates directly with standard PLC setups. Let me know if you would like me to share the technical data sheet or discuss sizing for your specific tank dimensions.&lt;/p&gt;
-      &lt;p style="margin-top:12pt;"&gt;We would be pleased to support your project and regular instrumentation requirements and provide further technical or commercial details based on your application.&lt;/p&gt;
-      &lt;p style="margin-top:12pt; margin-bottom:0;"&gt;Looking forward to your requirements.&lt;/p&gt;
-    &lt;/div&gt;
-    &lt;div class="product-image-wrap" style="background-color:#ffffff; padding:12pt 20pt 16pt 20pt; text-align:center;"&gt;
-      &lt;a href="https://www.sapconinstruments.com/products/vibrating-fork-level-switch-elixir" target="_blank"&gt;
-        &lt;img src="/images/image2.png" alt="Vibrating Fork (Elixir)" style="max-width:520px; width:100%; height:auto; border-radius:6px; border:1px solid #edf2f7; display:inline-block;"&gt;
-      &lt;/a&gt;
-    &lt;/div&gt;
-    &lt;div class="signature-card"&gt;
-      &lt;table class="sig-table"&gt;
-        &lt;tr&gt;
-          &lt;td class="sig-logo-td"&gt;
-            &lt;img src="/images/image1.png" alt="SAPCON Instruments Official Logo"&gt;
-          &lt;/td&gt;
-          &lt;td class="sig-info-td"&gt;
-            &lt;div class="sig-thanks"&gt;Thanks &amp;amp; Regards,&lt;/div&gt;
-            &lt;div class="sig-name"&gt;Elvis Joseph&lt;/div&gt;
-            &lt;div class="sig-desig"&gt;Regional Manager – South India Sales&lt;/div&gt;
-            &lt;div class="sig-company"&gt;SAPCON Instruments Pvt. Ltd.&lt;/div&gt;
-            &lt;div class="sig-contact"&gt;
-              P: 8871428228 / 0731-4757576, 75&lt;br&gt;
-              W: &lt;a href="https://www.sapconinstruments.com" class="sig-link" target="_blank"&gt;sapconinstruments.com&lt;/a&gt;
-            &lt;/div&gt;
-          &lt;/td&gt;
-        &lt;/tr&gt;
-      &lt;/table&gt;
-    &lt;/div&gt;
-    &lt;div class="footer-bar"&gt;
-      &lt;div&gt;&amp;copy; 2026 SAPCON Instruments. All rights reserved.&lt;/div&gt;
-      &lt;div&gt;Process Control Instrumentation &amp;bull; Indore, India&lt;/div&gt;
-    &lt;/div&gt;
-  &lt;/div&gt;
-&lt;/body&gt;
-&lt;/html&gt;
-</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Sent</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>16-Oct-2026 11:53 AM</t>
-        </is>
+    <row r="5" xml:space="preserve">
+      <c r="A5" t="str">
+        <v>Nextzee</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Raghav Tiwari</v>
+      </c>
+      <c r="C5" t="str">
+        <v>rt191708@gmail.com</v>
+      </c>
+      <c r="D5" t="str">
+        <v>we need elixer for silo liquid nature</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Level measurement enquiry for Nextzee silos</v>
+      </c>
+      <c r="F5" t="str" xml:space="preserve">
+        <v xml:space="preserve">&lt;!DOCTYPE html&gt;_x000d_
+&lt;html lang="en"&gt;_x000d_
+&lt;head&gt;_x000d_
+&lt;meta charset="UTF-8"&gt;_x000d_
+&lt;meta name="viewport" content="width=device-width, initial-scale=1.0"&gt;_x000d_
+&lt;title&gt;SAPCON Instruments&lt;/title&gt;_x000d_
+&lt;style type="text/css"&gt;_x000d_
+  body {_x000d_
+    margin: 0;_x000d_
+    padding: 20px 0;_x000d_
+    background-color: #f1f5f9;_x000d_
+    font-family: Arial, Helvetica, sans-serif;_x000d_
+    color: #2d3748;_x000d_
+    -webkit-font-smoothing: antialiased;_x000d_
+  }_x000d_
+  .email-container {_x000d_
+    max-width: 620px;_x000d_
+    margin: 0 auto;_x000d_
+    background-color: #ffffff;_x000d_
+    border: 1px solid #e2e8f0;_x000d_
+    border-radius: 8px;_x000d_
+    overflow: hidden;_x000d_
+    box-shadow: 0 4px 16px rgba(15, 44, 89, 0.08);_x000d_
+  }_x000d_
+  .email-body {_x000d_
+    padding: 24pt 24pt 14pt 24pt;_x000d_
+    font-size: 11pt;_x000d_
+    line-height: 1.5;_x000d_
+    color: #2d3748;_x000d_
+  }_x000d_
+  .email-body p {_x000d_
+    margin: 0 0 10pt 0;_x000d_
+  }_x000d_
+  .signature-card {_x000d_
+    background-color: #ffffff;_x000d_
+    border-top: 1px solid #e2e8f0;_x000d_
+    padding: 16pt 24pt;_x000d_
+  }_x000d_
+  .sig-table {_x000d_
+    width: 100%;_x000d_
+    border-collapse: collapse;_x000d_
+  }_x000d_
+  .sig-logo-td {_x000d_
+    width: 95px;_x000d_
+    vertical-align: middle;_x000d_
+    padding-right: 16pt;_x000d_
+    border-right: 1.5pt solid #0f2c59;_x000d_
+  }_x000d_
+  .sig-logo-td img {_x000d_
+    width: 88px;_x000d_
+    height: auto;_x000d_
+    display: block;_x000d_
+  }_x000d_
+  .sig-info-td {_x000d_
+    vertical-align: middle;_x000d_
+    padding-left: 16pt;_x000d_
+    font-size: 10pt;_x000d_
+    line-height: 1.35;_x000d_
+    color: #4a5568;_x000d_
+  }_x000d_
+  .sig-thanks {_x000d_
+    font-size: 10.5pt;_x000d_
+    color: #2d3748;_x000d_
+    margin-bottom: 2px;_x000d_
+  }_x000d_
+  .sig-name {_x000d_
+    font-size: 11pt;_x000d_
+    font-weight: 700;_x000d_
+    color: #0f2c59;_x000d_
+  }_x000d_
+  .sig-desig {_x000d_
+    font-size: 9.5pt;_x000d_
+    color: #4a5568;_x000d_
+    margin-bottom: 3px;_x000d_
+  }_x000d_
+  .sig-company {_x000d_
+    font-size: 10pt;_x000d_
+    font-weight: 700;_x000d_
+    color: #2d3748;_x000d_
+  }_x000d_
+  .sig-contact {_x000d_
+    font-size: 9pt;_x000d_
+    color: #4a5568;_x000d_
+    margin-top: 3px;_x000d_
+  }_x000d_
+  .sig-link {_x000d_
+    color: #0f2c59;_x000d_
+    text-decoration: underline;_x000d_
+    font-weight: 600;_x000d_
+  }_x000d_
+  .footer-bar {_x000d_
+    background-color: #f8fafc;_x000d_
+    border-top: 1px solid #e2e8f0;_x000d_
+    padding: 14pt 24pt;_x000d_
+    text-align: center;_x000d_
+    font-size: 9.5pt;_x000d_
+    color: #718096;_x000d_
+    line-height: 1.4;_x000d_
+  }_x000d_
+&lt;/style&gt;_x000d_
+&lt;/head&gt;_x000d_
+&lt;body&gt;_x000d_
+  &lt;div class="email-container"&gt;_x000d_
+    &lt;div class="email-body"&gt;_x000d_
+      &lt;p&gt;Dear Raghav Tiwari,&lt;/p&gt;_x000d_
+      &lt;p&gt;Greetings from &lt;strong&gt;SAPCON Instruments Pvt. Ltd.&lt;/strong&gt;&lt;/p&gt;_x000d_
+      &lt;p style="margin-top:12pt;"&gt;Please find attached our product details featuring the &lt;a href="https://www.sapconinstruments.com/products/vibrating-fork-level-switch-elixir" target="_blank" style="color:#0f2c59; font-weight:700; text-decoration:underline;"&gt;Vibrating Fork (Elixir)&lt;/a&gt; for Liquid level detection in industrial silos.&lt;/p&gt;_x000d_
+      &lt;p style="margin:12pt 0; line-height:1.5; color:#2d3748;"&gt;Hi Raghav, I understand you are looking for a reliable level switch to handle liquid applications in your silos. Our Elixir vibrating fork is ideally suited for this, offering dependable, no-moving-parts operation that resists buildup and integrates directly with standard PLC setups. Let me know if you would like me to share the technical data sheet or discuss sizing for your specific tank dimensions.&lt;/p&gt;_x000d_
+      &lt;p style="margin-top:12pt;"&gt;We would be pleased to support your project and regular instrumentation requirements and provide further technical or commercial details based on your application.&lt;/p&gt;_x000d_
+      &lt;p style="margin-top:12pt; margin-bottom:0;"&gt;Looking forward to your requirements.&lt;/p&gt;_x000d_
+    &lt;/div&gt;_x000d_
+_x000d_
+    _x000d_
+    &lt;div class="product-image-wrap" style="background-color:#ffffff; padding:12pt 20pt 16pt 20pt; text-align:center;"&gt;_x000d_
+      &lt;a href="https://www.sapconinstruments.com/products/vibrating-fork-level-switch-elixir" target="_blank"&gt;_x000d_
+        &lt;img src="/images/image2.png" alt="Vibrating Fork (Elixir)" style="max-width:520px; width:100%; height:auto; border-radius:6px; border:1px solid #edf2f7; display:inline-block;"&gt;_x000d_
+      &lt;/a&gt;_x000d_
+    &lt;/div&gt;_x000d_
+_x000d_
+_x000d_
+    &lt;div class="signature-card"&gt;_x000d_
+      &lt;table class="sig-table"&gt;_x000d_
+        &lt;tr&gt;_x000d_
+          &lt;td class="sig-logo-td"&gt;_x000d_
+            &lt;img src="/images/image1.png" alt="SAPCON Instruments Official Logo"&gt;_x000d_
+          &lt;/td&gt;_x000d_
+          &lt;td class="sig-info-td"&gt;_x000d_
+            &lt;div class="sig-thanks"&gt;Thanks &amp;amp; Regards,&lt;/div&gt;_x000d_
+            &lt;div class="sig-name"&gt;Elvis Joseph&lt;/div&gt;_x000d_
+            &lt;div class="sig-desig"&gt;Regional Manager – South India Sales&lt;/div&gt;_x000d_
+            &lt;div class="sig-company"&gt;SAPCON Instruments Pvt. Ltd.&lt;/div&gt;_x000d_
+            &lt;div class="sig-contact"&gt;_x000d_
+              P: 8871428228 / 0731-4757576, 75&lt;br&gt;_x000d_
+              W: &lt;a href="https://www.sapconinstruments.com" class="sig-link" target="_blank"&gt;sapconinstruments.com&lt;/a&gt;_x000d_
+            &lt;/div&gt;_x000d_
+          &lt;/td&gt;_x000d_
+        &lt;/tr&gt;_x000d_
+      &lt;/table&gt;_x000d_
+    &lt;/div&gt;_x000d_
+_x000d_
+    &lt;div class="footer-bar"&gt;_x000d_
+      &lt;div&gt;&amp;copy; 2026 SAPCON Instruments. All rights reserved.&lt;/div&gt;_x000d_
+      &lt;div&gt;Process Control Instrumentation &amp;bull; Indore, India&lt;/div&gt;_x000d_
+    &lt;/div&gt;_x000d_
+  &lt;/div&gt;_x000d_
+&lt;/body&gt;_x000d_
+&lt;/html&gt;_x000d_
+</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="H5" t="str">
+        <v>16-Oct-2026 11:53 AM</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>IMA</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Rahaber Raza</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>ramsharma9724@gmail.com</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>we need vital and elixer and RF admistance for my plant urgent basis</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Requirement for Vital, Elixir &amp; RF Admittance level instruments at IMA</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;!DOCTYPE html&gt;
+    <row r="6" xml:space="preserve">
+      <c r="A6" t="str">
+        <v>IMA</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Rahaber Raza</v>
+      </c>
+      <c r="C6" t="str">
+        <v>ramsharma9724@gmail.com</v>
+      </c>
+      <c r="D6" t="str">
+        <v>we need vital and elixer and RF admistance for my plant urgent basis</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Requirement for Vital, Elixir &amp; RF Admittance level instruments at IMA</v>
+      </c>
+      <c r="F6" t="str" xml:space="preserve">
+        <v xml:space="preserve">&lt;!DOCTYPE html&gt;
 &lt;html lang="en"&gt;
 &lt;head&gt;
 &lt;meta charset="UTF-8"&gt;
@@ -1372,45 +1283,33 @@
   &lt;/div&gt;
 &lt;/body&gt;
 &lt;/html&gt;
-</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Waiting for Approval</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Waiting for Approval</v>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Nextzee</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Raghav Tiwari</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>rt191708@gmail.com</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>we need elixer for silo liquid nature</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Level instrumentation enquiry for Nextzee</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;!DOCTYPE html&gt;
+    <row r="7" xml:space="preserve">
+      <c r="A7" t="str">
+        <v>Nextzee</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Raghav Tiwari</v>
+      </c>
+      <c r="C7" t="str">
+        <v>rt191708@gmail.com</v>
+      </c>
+      <c r="D7" t="str">
+        <v>we need elixer for silo liquid nature</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Level instrumentation enquiry for Nextzee</v>
+      </c>
+      <c r="F7" t="str" xml:space="preserve">
+        <v xml:space="preserve">&lt;!DOCTYPE html&gt;
 &lt;html lang="en"&gt;
 &lt;head&gt;
 &lt;meta charset="UTF-8"&gt;
@@ -1552,45 +1451,33 @@
   &lt;/div&gt;
 &lt;/body&gt;
 &lt;/html&gt;
-</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Waiting for Approval</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Waiting for Approval</v>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>IMA</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Rahaber Raza</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>ramsharma9724@gmail.com</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>we need vital and elixer and RF admistance for my plant urgent basis</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Level instrumentation enquiry for IMA</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;!DOCTYPE html&gt;
+    <row r="8" xml:space="preserve">
+      <c r="A8" t="str">
+        <v>IMA</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Rahaber Raza</v>
+      </c>
+      <c r="C8" t="str">
+        <v>ramsharma9724@gmail.com</v>
+      </c>
+      <c r="D8" t="str">
+        <v>we need vital and elixer and RF admistance for my plant urgent basis</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Level instrumentation enquiry for IMA</v>
+      </c>
+      <c r="F8" t="str" xml:space="preserve">
+        <v xml:space="preserve">&lt;!DOCTYPE html&gt;
 &lt;html lang="en"&gt;
 &lt;head&gt;
 &lt;meta charset="UTF-8"&gt;
@@ -1732,45 +1619,33 @@
   &lt;/div&gt;
 &lt;/body&gt;
 &lt;/html&gt;
-</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Waiting for Approval</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Waiting for Approval</v>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Nextzee</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Raghav Tiwari</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>rt191708@gmail.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>we need elixer for silo liquid nature</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Level instrumentation enquiry for Nextzee</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;!DOCTYPE html&gt;
+    <row r="9" xml:space="preserve">
+      <c r="A9" t="str">
+        <v>Nextzee</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Raghav Tiwari</v>
+      </c>
+      <c r="C9" t="str">
+        <v>rt191708@gmail.com</v>
+      </c>
+      <c r="D9" t="str">
+        <v>we need elixer for silo liquid nature</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Level instrumentation enquiry for Nextzee</v>
+      </c>
+      <c r="F9" t="str" xml:space="preserve">
+        <v xml:space="preserve">&lt;!DOCTYPE html&gt;
 &lt;html lang="en"&gt;
 &lt;head&gt;
 &lt;meta charset="UTF-8"&gt;
@@ -1912,45 +1787,33 @@
   &lt;/div&gt;
 &lt;/body&gt;
 &lt;/html&gt;
-</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Waiting for Approval</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Waiting for Approval</v>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>IMA</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Rahaber Raza</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>ramsharma9724@gmail.com</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>we need vital and elixer and RF admistance for my plant urgent basis</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Level instrumentation requirements for IMA - Sapcon Instruments</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;!DOCTYPE html&gt;
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str">
+        <v>IMA</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Rahaber Raza</v>
+      </c>
+      <c r="C10" t="str">
+        <v>ramsharma9724@gmail.com</v>
+      </c>
+      <c r="D10" t="str">
+        <v>we need vital and elixer and RF admistance for my plant urgent basis</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Level instrumentation requirements for IMA - Sapcon Instruments</v>
+      </c>
+      <c r="F10" t="str" xml:space="preserve">
+        <v xml:space="preserve">&lt;!DOCTYPE html&gt;
 &lt;html lang="en"&gt;
 &lt;head&gt;
 &lt;meta charset="UTF-8"&gt;
@@ -2092,229 +1955,206 @@
   &lt;/div&gt;
 &lt;/body&gt;
 &lt;/html&gt;
-</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Waiting for Approval</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Waiting for Approval</v>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Nextzee</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Raghav Tiwari</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>rt191708@gmail.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>we need elixer for silo liquid nature</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Level instrumentation for Nextzee silo application</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;!DOCTYPE html&gt;
-&lt;html lang="en"&gt;
-&lt;head&gt;
-&lt;meta charset="UTF-8"&gt;
-&lt;meta name="viewport" content="width=device-width, initial-scale=1.0"&gt;
-&lt;title&gt;SAPCON Instruments&lt;/title&gt;
-&lt;style type="text/css"&gt;
-  body {
-    margin: 0;
-    padding: 20px 0;
-    background-color: #f1f5f9;
-    font-family: Arial, Helvetica, sans-serif;
-    color: #2d3748;
-    -webkit-font-smoothing: antialiased;
-  }
-  .email-container {
-    max-width: 620px;
-    margin: 0 auto;
-    background-color: #ffffff;
-    border: 1px solid #e2e8f0;
-    border-radius: 8px;
-    overflow: hidden;
-    box-shadow: 0 4px 16px rgba(15, 44, 89, 0.08);
-  }
-  .email-body {
-    padding: 24pt 24pt 14pt 24pt;
-    font-size: 11pt;
-    line-height: 1.5;
-    color: #2d3748;
-  }
-  .email-body p {
-    margin: 0 0 10pt 0;
-  }
-  .signature-card {
-    background-color: #ffffff;
-    border-top: 1px solid #e2e8f0;
-    padding: 16pt 24pt;
-  }
-  .sig-table {
-    width: 100%;
-    border-collapse: collapse;
-  }
-  .sig-logo-td {
-    width: 95px;
-    vertical-align: middle;
-    padding-right: 16pt;
-    border-right: 1.5pt solid #0f2c59;
-  }
-  .sig-logo-td img {
-    width: 88px;
-    height: auto;
-    display: block;
-  }
-  .sig-info-td {
-    vertical-align: middle;
-    padding-left: 16pt;
-    font-size: 10pt;
-    line-height: 1.35;
-    color: #4a5568;
-  }
-  .sig-thanks {
-    font-size: 10.5pt;
-    color: #2d3748;
-    margin-bottom: 2px;
-  }
-  .sig-name {
-    font-size: 11pt;
-    font-weight: 700;
-    color: #0f2c59;
-  }
-  .sig-desig {
-    font-size: 9.5pt;
-    color: #4a5568;
-    margin-bottom: 3px;
-  }
-  .sig-company {
-    font-size: 10pt;
-    font-weight: 700;
-    color: #2d3748;
-  }
-  .sig-contact {
-    font-size: 9pt;
-    color: #4a5568;
-    margin-top: 3px;
-  }
-  .sig-link {
-    color: #0f2c59;
-    text-decoration: underline;
-    font-weight: 600;
-  }
-  .footer-bar {
-    background-color: #f8fafc;
-    border-top: 1px solid #e2e8f0;
-    padding: 14pt 24pt;
-    text-align: center;
-    font-size: 9.5pt;
-    color: #718096;
-    line-height: 1.4;
-  }
-&lt;/style&gt;
-&lt;/head&gt;
-&lt;body&gt;
-  &lt;div class="email-container"&gt;
-    &lt;div class="email-body"&gt;
-      &lt;p&gt;Dear Raghav Tiwari,&lt;/p&gt;
-      &lt;p&gt;Greetings from &lt;strong&gt;SAPCON Instruments Pvt. Ltd.&lt;/strong&gt;&lt;/p&gt;
-      &lt;p style="margin-top:12pt;"&gt;Please find attached our product details featuring the &lt;a href="https://www.sapconinstruments.com/products/vibrating-fork-level-switch-elixir" target="_blank" style="color:#0f2c59; font-weight:700; text-decoration:underline;"&gt;Vibrating Fork (Elixir)&lt;/a&gt; for Liquid Level Detection in Silos &amp; Tanks.&lt;/p&gt;
-      &lt;p style="margin:12pt 0; line-height:1.5; color:#2d3748;"&gt;Hi Raghav, understood your requirement for a reliable liquid level switch for your silo application. Our Vibrating Fork model 'Elixir' works well for clean and viscous liquids with its tuning fork design, offering solid immunity against buildup and direct 4-20mA or relay integration with your PLC. Let me know if you would like me to share the technical data sheet or discuss sizing for your specific tank dimensions.&lt;/p&gt;
-      &lt;p style="margin-top:12pt;"&gt;We would be pleased to support your project and regular instrumentation requirements and provide further technical or commercial details based on your application.&lt;/p&gt;
-      &lt;p style="margin-top:12pt; margin-bottom:0;"&gt;Looking forward to your requirements.&lt;/p&gt;
-    &lt;/div&gt;
-    &lt;div class="product-image-wrap" style="background-color:#ffffff; padding:12pt 20pt 16pt 20pt; text-align:center;"&gt;
-      &lt;a href="https://www.sapconinstruments.com/products/vibrating-fork-level-switch-elixir" target="_blank"&gt;
-        &lt;img src="/images/image2.png" alt="Vibrating Fork (Elixir)" style="max-width:520px; width:100%; height:auto; border-radius:6px; border:1px solid #edf2f7; display:inline-block;"&gt;
-      &lt;/a&gt;
-    &lt;/div&gt;
-    &lt;div class="signature-card"&gt;
-      &lt;table class="sig-table"&gt;
-        &lt;tr&gt;
-          &lt;td class="sig-logo-td"&gt;
-            &lt;img src="/images/image1.png" alt="SAPCON Instruments Official Logo"&gt;
-          &lt;/td&gt;
-          &lt;td class="sig-info-td"&gt;
-            &lt;div class="sig-thanks"&gt;Thanks &amp;amp; Regards,&lt;/div&gt;
-            &lt;div class="sig-name"&gt;Elvis Joseph&lt;/div&gt;
-            &lt;div class="sig-desig"&gt;Regional Manager – South India Sales&lt;/div&gt;
-            &lt;div class="sig-company"&gt;SAPCON Instruments Pvt. Ltd.&lt;/div&gt;
-            &lt;div class="sig-contact"&gt;
-              P: 8871428228 / 0731-4757576, 75&lt;br&gt;
-              W: &lt;a href="https://www.sapconinstruments.com" class="sig-link" target="_blank"&gt;sapconinstruments.com&lt;/a&gt;
-            &lt;/div&gt;
-          &lt;/td&gt;
-        &lt;/tr&gt;
-      &lt;/table&gt;
-    &lt;/div&gt;
-    &lt;div class="footer-bar"&gt;
-      &lt;div&gt;&amp;copy; 2026 SAPCON Instruments. All rights reserved.&lt;/div&gt;
-      &lt;div&gt;Process Control Instrumentation &amp;bull; Indore, India&lt;/div&gt;
-    &lt;/div&gt;
-  &lt;/div&gt;
-&lt;/body&gt;
-&lt;/html&gt;
-</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Sent</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>16-Oct-2026 03:17 PM</t>
-        </is>
+    <row r="11" xml:space="preserve">
+      <c r="A11" t="str">
+        <v>Nextzee</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Raghav Tiwari</v>
+      </c>
+      <c r="C11" t="str">
+        <v>rt191708@gmail.com</v>
+      </c>
+      <c r="D11" t="str">
+        <v>we need elixer for silo liquid nature</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Level instrumentation for Nextzee silo application</v>
+      </c>
+      <c r="F11" t="str" xml:space="preserve">
+        <v xml:space="preserve">&lt;!DOCTYPE html&gt;_x000d_
+&lt;html lang="en"&gt;_x000d_
+&lt;head&gt;_x000d_
+&lt;meta charset="UTF-8"&gt;_x000d_
+&lt;meta name="viewport" content="width=device-width, initial-scale=1.0"&gt;_x000d_
+&lt;title&gt;SAPCON Instruments&lt;/title&gt;_x000d_
+&lt;style type="text/css"&gt;_x000d_
+  body {_x000d_
+    margin: 0;_x000d_
+    padding: 20px 0;_x000d_
+    background-color: #f1f5f9;_x000d_
+    font-family: Arial, Helvetica, sans-serif;_x000d_
+    color: #2d3748;_x000d_
+    -webkit-font-smoothing: antialiased;_x000d_
+  }_x000d_
+  .email-container {_x000d_
+    max-width: 620px;_x000d_
+    margin: 0 auto;_x000d_
+    background-color: #ffffff;_x000d_
+    border: 1px solid #e2e8f0;_x000d_
+    border-radius: 8px;_x000d_
+    overflow: hidden;_x000d_
+    box-shadow: 0 4px 16px rgba(15, 44, 89, 0.08);_x000d_
+  }_x000d_
+  .email-body {_x000d_
+    padding: 24pt 24pt 14pt 24pt;_x000d_
+    font-size: 11pt;_x000d_
+    line-height: 1.5;_x000d_
+    color: #2d3748;_x000d_
+  }_x000d_
+  .email-body p {_x000d_
+    margin: 0 0 10pt 0;_x000d_
+  }_x000d_
+  .signature-card {_x000d_
+    background-color: #ffffff;_x000d_
+    border-top: 1px solid #e2e8f0;_x000d_
+    padding: 16pt 24pt;_x000d_
+  }_x000d_
+  .sig-table {_x000d_
+    width: 100%;_x000d_
+    border-collapse: collapse;_x000d_
+  }_x000d_
+  .sig-logo-td {_x000d_
+    width: 95px;_x000d_
+    vertical-align: middle;_x000d_
+    padding-right: 16pt;_x000d_
+    border-right: 1.5pt solid #0f2c59;_x000d_
+  }_x000d_
+  .sig-logo-td img {_x000d_
+    width: 88px;_x000d_
+    height: auto;_x000d_
+    display: block;_x000d_
+  }_x000d_
+  .sig-info-td {_x000d_
+    vertical-align: middle;_x000d_
+    padding-left: 16pt;_x000d_
+    font-size: 10pt;_x000d_
+    line-height: 1.35;_x000d_
+    color: #4a5568;_x000d_
+  }_x000d_
+  .sig-thanks {_x000d_
+    font-size: 10.5pt;_x000d_
+    color: #2d3748;_x000d_
+    margin-bottom: 2px;_x000d_
+  }_x000d_
+  .sig-name {_x000d_
+    font-size: 11pt;_x000d_
+    font-weight: 700;_x000d_
+    color: #0f2c59;_x000d_
+  }_x000d_
+  .sig-desig {_x000d_
+    font-size: 9.5pt;_x000d_
+    color: #4a5568;_x000d_
+    margin-bottom: 3px;_x000d_
+  }_x000d_
+  .sig-company {_x000d_
+    font-size: 10pt;_x000d_
+    font-weight: 700;_x000d_
+    color: #2d3748;_x000d_
+  }_x000d_
+  .sig-contact {_x000d_
+    font-size: 9pt;_x000d_
+    color: #4a5568;_x000d_
+    margin-top: 3px;_x000d_
+  }_x000d_
+  .sig-link {_x000d_
+    color: #0f2c59;_x000d_
+    text-decoration: underline;_x000d_
+    font-weight: 600;_x000d_
+  }_x000d_
+  .footer-bar {_x000d_
+    background-color: #f8fafc;_x000d_
+    border-top: 1px solid #e2e8f0;_x000d_
+    padding: 14pt 24pt;_x000d_
+    text-align: center;_x000d_
+    font-size: 9.5pt;_x000d_
+    color: #718096;_x000d_
+    line-height: 1.4;_x000d_
+  }_x000d_
+&lt;/style&gt;_x000d_
+&lt;/head&gt;_x000d_
+&lt;body&gt;_x000d_
+  &lt;div class="email-container"&gt;_x000d_
+    &lt;div class="email-body"&gt;_x000d_
+      &lt;p&gt;Dear Raghav Tiwari,&lt;/p&gt;_x000d_
+      &lt;p&gt;Greetings from &lt;strong&gt;SAPCON Instruments Pvt. Ltd.&lt;/strong&gt;&lt;/p&gt;_x000d_
+      &lt;p style="margin-top:12pt;"&gt;Please find attached our product details featuring the &lt;a href="https://www.sapconinstruments.com/products/vibrating-fork-level-switch-elixir" target="_blank" style="color:#0f2c59; font-weight:700; text-decoration:underline;"&gt;Vibrating Fork (Elixir)&lt;/a&gt; for Liquid Level Detection in Silos &amp; Tanks.&lt;/p&gt;_x000d_
+      &lt;p style="margin:12pt 0; line-height:1.5; color:#2d3748;"&gt;Hi Raghav, understood your requirement for a reliable liquid level switch for your silo application. Our Vibrating Fork model 'Elixir' works well for clean and viscous liquids with its tuning fork design, offering solid immunity against buildup and direct 4-20mA or relay integration with your PLC. Let me know if you would like me to share the technical data sheet or discuss sizing for your specific tank dimensions.&lt;/p&gt;_x000d_
+      &lt;p style="margin-top:12pt;"&gt;We would be pleased to support your project and regular instrumentation requirements and provide further technical or commercial details based on your application.&lt;/p&gt;_x000d_
+      &lt;p style="margin-top:12pt; margin-bottom:0;"&gt;Looking forward to your requirements.&lt;/p&gt;_x000d_
+    &lt;/div&gt;_x000d_
+_x000d_
+    _x000d_
+    &lt;div class="product-image-wrap" style="background-color:#ffffff; padding:12pt 20pt 16pt 20pt; text-align:center;"&gt;_x000d_
+      &lt;a href="https://www.sapconinstruments.com/products/vibrating-fork-level-switch-elixir" target="_blank"&gt;_x000d_
+        &lt;img src="/images/image2.png" alt="Vibrating Fork (Elixir)" style="max-width:520px; width:100%; height:auto; border-radius:6px; border:1px solid #edf2f7; display:inline-block;"&gt;_x000d_
+      &lt;/a&gt;_x000d_
+    &lt;/div&gt;_x000d_
+_x000d_
+_x000d_
+    &lt;div class="signature-card"&gt;_x000d_
+      &lt;table class="sig-table"&gt;_x000d_
+        &lt;tr&gt;_x000d_
+          &lt;td class="sig-logo-td"&gt;_x000d_
+            &lt;img src="/images/image1.png" alt="SAPCON Instruments Official Logo"&gt;_x000d_
+          &lt;/td&gt;_x000d_
+          &lt;td class="sig-info-td"&gt;_x000d_
+            &lt;div class="sig-thanks"&gt;Thanks &amp;amp; Regards,&lt;/div&gt;_x000d_
+            &lt;div class="sig-name"&gt;Elvis Joseph&lt;/div&gt;_x000d_
+            &lt;div class="sig-desig"&gt;Regional Manager – South India Sales&lt;/div&gt;_x000d_
+            &lt;div class="sig-company"&gt;SAPCON Instruments Pvt. Ltd.&lt;/div&gt;_x000d_
+            &lt;div class="sig-contact"&gt;_x000d_
+              P: 8871428228 / 0731-4757576, 75&lt;br&gt;_x000d_
+              W: &lt;a href="https://www.sapconinstruments.com" class="sig-link" target="_blank"&gt;sapconinstruments.com&lt;/a&gt;_x000d_
+            &lt;/div&gt;_x000d_
+          &lt;/td&gt;_x000d_
+        &lt;/tr&gt;_x000d_
+      &lt;/table&gt;_x000d_
+    &lt;/div&gt;_x000d_
+_x000d_
+    &lt;div class="footer-bar"&gt;_x000d_
+      &lt;div&gt;&amp;copy; 2026 SAPCON Instruments. All rights reserved.&lt;/div&gt;_x000d_
+      &lt;div&gt;Process Control Instrumentation &amp;bull; Indore, India&lt;/div&gt;_x000d_
+    &lt;/div&gt;_x000d_
+  &lt;/div&gt;_x000d_
+&lt;/body&gt;_x000d_
+&lt;/html&gt;_x000d_
+</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="H11" t="str">
+        <v>16-Oct-2026 03:17 PM</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>IMA</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Rahaber Raza</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>ramsharma9724@gmail.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>we need vital and elixer and RF admistance for my plant urgent basis</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Level instrumentation enquiry for IMA</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;!DOCTYPE html&gt;
+    <row r="12" xml:space="preserve">
+      <c r="A12" t="str">
+        <v>IMA</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Rahaber Raza</v>
+      </c>
+      <c r="C12" t="str">
+        <v>ramsharma9724@gmail.com</v>
+      </c>
+      <c r="D12" t="str">
+        <v>we need vital and elixer and RF admistance for my plant urgent basis</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Level instrumentation enquiry for IMA</v>
+      </c>
+      <c r="F12" t="str" xml:space="preserve">
+        <v xml:space="preserve">&lt;!DOCTYPE html&gt;
 &lt;html lang="en"&gt;
 &lt;head&gt;
 &lt;meta charset="UTF-8"&gt;
@@ -2456,41 +2296,33 @@
   &lt;/div&gt;
 &lt;/body&gt;
 &lt;/html&gt;
-</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Waiting for Approval</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Waiting for Approval</v>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>nextzee</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>rt191708@gmail.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>vital enquiry</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Level instrumentation enquiry for nextzee</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;!DOCTYPE html&gt;
+    <row r="13" xml:space="preserve">
+      <c r="A13" t="str">
+        <v>nextzee</v>
+      </c>
+      <c r="B13" t="str">
+        <v/>
+      </c>
+      <c r="C13" t="str">
+        <v>rt191708@gmail.com</v>
+      </c>
+      <c r="D13" t="str">
+        <v>vital enquiry</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Level instrumentation enquiry for nextzee</v>
+      </c>
+      <c r="F13" t="str" xml:space="preserve">
+        <v xml:space="preserve">&lt;!DOCTYPE html&gt;
 &lt;html lang="en"&gt;
 &lt;head&gt;
 &lt;meta charset="UTF-8"&gt;
@@ -2632,45 +2464,33 @@
   &lt;/div&gt;
 &lt;/body&gt;
 &lt;/html&gt;
-</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Waiting for Approval</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Waiting for Approval</v>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Nextzee</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Raghav Tiwari</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>rt191708@gmail.com</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>we need elixer for silo liquid nature</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Level instrumentation enquiry for Nextzee silos</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;!DOCTYPE html&gt;
+    <row r="14" xml:space="preserve">
+      <c r="A14" t="str">
+        <v>Nextzee</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Raghav Tiwari</v>
+      </c>
+      <c r="C14" t="str">
+        <v>rt191708@gmail.com</v>
+      </c>
+      <c r="D14" t="str">
+        <v>we need elixer for silo liquid nature</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Level instrumentation enquiry for Nextzee silos</v>
+      </c>
+      <c r="F14" t="str" xml:space="preserve">
+        <v xml:space="preserve">&lt;!DOCTYPE html&gt;
 &lt;html lang="en"&gt;
 &lt;head&gt;
 &lt;meta charset="UTF-8"&gt;
@@ -2812,45 +2632,33 @@
   &lt;/div&gt;
 &lt;/body&gt;
 &lt;/html&gt;
-</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Waiting for Approval</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Waiting for Approval</v>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>IMA</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Rahaber Raza</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>ramsharma9724@gmail.com</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>we need vital and elixer and RF admistance for my plant urgent basis</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Level instrumentation requirement for IMA plant - SAPCON</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;!DOCTYPE html&gt;
+    <row r="15" xml:space="preserve">
+      <c r="A15" t="str">
+        <v>IMA</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Rahaber Raza</v>
+      </c>
+      <c r="C15" t="str">
+        <v>ramsharma9724@gmail.com</v>
+      </c>
+      <c r="D15" t="str">
+        <v>we need vital and elixer and RF admistance for my plant urgent basis</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Level instrumentation requirement for IMA plant - SAPCON</v>
+      </c>
+      <c r="F15" t="str" xml:space="preserve">
+        <v xml:space="preserve">&lt;!DOCTYPE html&gt;
 &lt;html lang="en"&gt;
 &lt;head&gt;
 &lt;meta charset="UTF-8"&gt;
@@ -2992,41 +2800,33 @@
   &lt;/div&gt;
 &lt;/body&gt;
 &lt;/html&gt;
-</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Waiting for Approval</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Waiting for Approval</v>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>nextzee</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>rt191708@gmail.com</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>hello</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Level instrumentation enquiry for nextzee</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;!DOCTYPE html&gt;
+    <row r="16" xml:space="preserve">
+      <c r="A16" t="str">
+        <v>nextzee</v>
+      </c>
+      <c r="B16" t="str">
+        <v/>
+      </c>
+      <c r="C16" t="str">
+        <v>rt191708@gmail.com</v>
+      </c>
+      <c r="D16" t="str">
+        <v>hello</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Level instrumentation enquiry for nextzee</v>
+      </c>
+      <c r="F16" t="str" xml:space="preserve">
+        <v xml:space="preserve">&lt;!DOCTYPE html&gt;
 &lt;html lang="en"&gt;
 &lt;head&gt;
 &lt;meta charset="UTF-8"&gt;
@@ -3172,45 +2972,33 @@
   &lt;/div&gt;
 &lt;/body&gt;
 &lt;/html&gt;
-</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Sent</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>16-Oct-2026 04:06 PM</t>
-        </is>
+</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="H16" t="str">
+        <v>16-Oct-2026 04:06 PM</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>codex</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>krishnadas199227@gmail.com</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>what is vital</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Technical details: Level instrumentation for codex utility &amp; storage tanks</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;!DOCTYPE html&gt;
+    <row r="17" xml:space="preserve">
+      <c r="A17" t="str">
+        <v>codex</v>
+      </c>
+      <c r="B17" t="str">
+        <v/>
+      </c>
+      <c r="C17" t="str">
+        <v>krishnadas199227@gmail.com</v>
+      </c>
+      <c r="D17" t="str">
+        <v>what is vital</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Technical details: Level instrumentation for codex utility &amp; storage tanks</v>
+      </c>
+      <c r="F17" t="str" xml:space="preserve">
+        <v xml:space="preserve">&lt;!DOCTYPE html&gt;
 &lt;html lang="en"&gt;
 &lt;head&gt;
 &lt;meta charset="UTF-8"&gt;
@@ -3352,41 +3140,33 @@
   &lt;/div&gt;
 &lt;/body&gt;
 &lt;/html&gt;
-</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Send Failed: GOOGLE_AUTH_REQUIRED: Please sign in with Google in the top bar before sending.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Send Failed: GOOGLE_AUTH_REQUIRED: Please sign in with Google in the top bar before sending.</v>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>codex</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>krishnadas199227@gmail.com</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>what is vital</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Level instrumentation enquiry for codex</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;!DOCTYPE html&gt;
+    <row r="18" xml:space="preserve">
+      <c r="A18" t="str">
+        <v>codex</v>
+      </c>
+      <c r="B18" t="str">
+        <v/>
+      </c>
+      <c r="C18" t="str">
+        <v>krishnadas199227@gmail.com</v>
+      </c>
+      <c r="D18" t="str">
+        <v>what is vital</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Level instrumentation enquiry for codex</v>
+      </c>
+      <c r="F18" t="str" xml:space="preserve">
+        <v xml:space="preserve">&lt;!DOCTYPE html&gt;
 &lt;html lang="en"&gt;
 &lt;head&gt;
 &lt;meta charset="UTF-8"&gt;
@@ -3528,17 +3308,854 @@
   &lt;/div&gt;
 &lt;/body&gt;
 &lt;/html&gt;
-</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Waiting for Approval</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Waiting for Approval</v>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19" xml:space="preserve">
+      <c r="A19" t="str">
+        <v>shyam and corporations</v>
+      </c>
+      <c r="B19" t="str">
+        <v/>
+      </c>
+      <c r="C19" t="str">
+        <v>rt191708@gmail.com</v>
+      </c>
+      <c r="D19" t="str">
+        <v>hello</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Technical details: RF Admittance Level Switch for shyam and corporations</v>
+      </c>
+      <c r="F19" t="str" xml:space="preserve">
+        <v xml:space="preserve">&lt;!DOCTYPE html&gt;
+&lt;html lang="en"&gt;
+&lt;head&gt;
+&lt;meta charset="UTF-8"&gt;
+&lt;meta name="viewport" content="width=device-width, initial-scale=1.0"&gt;
+&lt;title&gt;SAPCON Instruments&lt;/title&gt;
+&lt;style type="text/css"&gt;
+  body {
+    margin: 0;
+    padding: 20px 0;
+    background-color: #f1f5f9;
+    font-family: Arial, Helvetica, sans-serif;
+    color: #2d3748;
+    -webkit-font-smoothing: antialiased;
+  }
+  .email-container {
+    max-width: 620px;
+    margin: 0 auto;
+    background-color: #ffffff;
+    border: 1px solid #e2e8f0;
+    border-radius: 8px;
+    overflow: hidden;
+    box-shadow: 0 4px 16px rgba(15, 44, 89, 0.08);
+  }
+  .email-body {
+    padding: 24pt 24pt 14pt 24pt;
+    font-size: 11pt;
+    line-height: 1.5;
+    color: #2d3748;
+  }
+  .email-body p {
+    margin: 0 0 10pt 0;
+  }
+  .signature-card {
+    background-color: #ffffff;
+    border-top: 1px solid #e2e8f0;
+    padding: 16pt 24pt;
+  }
+  .sig-table {
+    width: 100%;
+    border-collapse: collapse;
+  }
+  .sig-logo-td {
+    width: 95px;
+    vertical-align: middle;
+    padding-right: 16pt;
+    border-right: 1.5pt solid #0f2c59;
+  }
+  .sig-logo-td img {
+    width: 88px;
+    height: auto;
+    display: block;
+  }
+  .sig-info-td {
+    vertical-align: middle;
+    padding-left: 16pt;
+    font-size: 10pt;
+    line-height: 1.35;
+    color: #4a5568;
+  }
+  .sig-thanks {
+    font-size: 10.5pt;
+    color: #2d3748;
+    margin-bottom: 2px;
+  }
+  .sig-name {
+    font-size: 11pt;
+    font-weight: 700;
+    color: #0f2c59;
+  }
+  .sig-desig {
+    font-size: 9.5pt;
+    color: #4a5568;
+    margin-bottom: 3px;
+  }
+  .sig-company {
+    font-size: 10pt;
+    font-weight: 700;
+    color: #2d3748;
+  }
+  .sig-contact {
+    font-size: 9pt;
+    color: #4a5568;
+    margin-top: 3px;
+  }
+  .sig-link {
+    color: #0f2c59;
+    text-decoration: underline;
+    font-weight: 600;
+  }
+  .footer-bar {
+    background-color: #f8fafc;
+    border-top: 1px solid #e2e8f0;
+    padding: 14pt 24pt;
+    text-align: center;
+    font-size: 9.5pt;
+    color: #718096;
+    line-height: 1.4;
+  }
+&lt;/style&gt;
+&lt;/head&gt;
+&lt;body&gt;
+  &lt;div class="email-container"&gt;
+    &lt;div class="email-body"&gt;
+      &lt;p&gt;Dear Plant Engineering &amp; Procurement Team, shyam and corporations,&lt;/p&gt;
+      &lt;p&gt;Greetings from &lt;strong&gt;SAPCON Instruments Pvt. Ltd.&lt;/strong&gt;&lt;/p&gt;
+      &lt;p style="margin-top:12pt;"&gt;Please find attached our product details featuring the &lt;a href="https://www.sapconinstruments.com/products/rf-admittance-level-switch-sla" target="_blank" style="color:#0f2c59; font-weight:700; text-decoration:underline;"&gt;RF Admittance Level Switch (SLA)&lt;/a&gt; for Material coating and buildup immunity for bulk solids, fly ash, cement, coal, or viscous slurry applications..&lt;/p&gt;
+      &lt;p style="margin:12pt 0; line-height:1.5; color:#2d3748;"&gt;Noting your plant engineering requirements at shyam and corporations, our RF Admittance Level Switch is well-suited to handle severe material buildup without false triggering. The design offers reliable point-level detection with 2-wire loop or relay output options that easily integrate into your existing PLC panels. Let me know if you would like me to share standard GA drawings, wiring schematics, or discuss sizing over a quick call.&lt;/p&gt;
+      &lt;p style="margin-top:12pt;"&gt;We would be pleased to support your project and regular instrumentation requirements and provide further technical or commercial details based on your application.&lt;/p&gt;
+      &lt;p style="margin-top:12pt; margin-bottom:0;"&gt;Looking forward to your requirements.&lt;/p&gt;
+    &lt;/div&gt;
+    &lt;div class="product-image-wrap" style="background-color:#ffffff; padding:12pt 20pt 16pt 20pt; text-align:center;"&gt;
+      &lt;a href="https://www.sapconinstruments.com/products/rf-admittance-level-switch-sla" target="_blank"&gt;
+        &lt;img src="/images/image2.png" alt="RF Admittance Level Switch (SLA)" style="max-width:520px; width:100%; height:auto; border-radius:6px; border:1px solid #edf2f7; display:inline-block;"&gt;
+      &lt;/a&gt;
+    &lt;/div&gt;
+    &lt;div class="signature-card"&gt;
+      &lt;table class="sig-table"&gt;
+        &lt;tr&gt;
+          &lt;td class="sig-logo-td"&gt;
+            &lt;img src="/images/image1.png" alt="SAPCON Instruments Official Logo"&gt;
+          &lt;/td&gt;
+          &lt;td class="sig-info-td"&gt;
+            &lt;div class="sig-thanks"&gt;Thanks &amp;amp; Regards,&lt;/div&gt;
+            &lt;div class="sig-name"&gt;Elvis Joseph&lt;/div&gt;
+            &lt;div class="sig-desig"&gt;Regional Manager – South India Sales&lt;/div&gt;
+            &lt;div class="sig-company"&gt;SAPCON Instruments Pvt. Ltd.&lt;/div&gt;
+            &lt;div class="sig-contact"&gt;
+              P: 8871428228 / 0731-4757576, 75&lt;br&gt;
+              W: &lt;a href="https://www.sapconinstruments.com" class="sig-link" target="_blank"&gt;sapconinstruments.com&lt;/a&gt;
+            &lt;/div&gt;
+          &lt;/td&gt;
+        &lt;/tr&gt;
+      &lt;/table&gt;
+    &lt;/div&gt;
+    &lt;div class="footer-bar"&gt;
+      &lt;div&gt;&amp;copy; 2026 SAPCON Instruments. All rights reserved.&lt;/div&gt;
+      &lt;div&gt;Process Control Instrumentation &amp;bull; Indore, India&lt;/div&gt;
+    &lt;/div&gt;
+  &lt;/div&gt;
+&lt;/body&gt;
+&lt;/html&gt;
+</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="H19" t="str">
+        <v>16-Oct-2026 06:41 PM</v>
+      </c>
+    </row>
+    <row r="20" xml:space="preserve">
+      <c r="A20" t="str">
+        <v>Nextzee</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Raghav Tiwari</v>
+      </c>
+      <c r="C20" t="str">
+        <v>rt191708@gmail.com</v>
+      </c>
+      <c r="D20" t="str">
+        <v>we need elixer for silo liquid nature</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Sapcon Elixir level switch details for Nextzee liquid silo</v>
+      </c>
+      <c r="F20" t="str" xml:space="preserve">
+        <v xml:space="preserve">&lt;!DOCTYPE html&gt;
+&lt;html lang="en"&gt;
+&lt;head&gt;
+&lt;meta charset="UTF-8"&gt;
+&lt;meta name="viewport" content="width=device-width, initial-scale=1.0"&gt;
+&lt;title&gt;SAPCON Instruments&lt;/title&gt;
+&lt;style type="text/css"&gt;
+  body {
+    margin: 0;
+    padding: 20px 0;
+    background-color: #f1f5f9;
+    font-family: Arial, Helvetica, sans-serif;
+    color: #2d3748;
+    -webkit-font-smoothing: antialiased;
+  }
+  .email-container {
+    max-width: 620px;
+    margin: 0 auto;
+    background-color: #ffffff;
+    border: 1px solid #e2e8f0;
+    border-radius: 8px;
+    overflow: hidden;
+    box-shadow: 0 4px 16px rgba(15, 44, 89, 0.08);
+  }
+  .email-body {
+    padding: 24pt 24pt 14pt 24pt;
+    font-size: 11pt;
+    line-height: 1.5;
+    color: #2d3748;
+  }
+  .email-body p {
+    margin: 0 0 10pt 0;
+  }
+  .signature-card {
+    background-color: #ffffff;
+    border-top: 1px solid #e2e8f0;
+    padding: 16pt 24pt;
+  }
+  .sig-table {
+    width: 100%;
+    border-collapse: collapse;
+  }
+  .sig-logo-td {
+    width: 95px;
+    vertical-align: middle;
+    padding-right: 16pt;
+    border-right: 1.5pt solid #0f2c59;
+  }
+  .sig-logo-td img {
+    width: 88px;
+    height: auto;
+    display: block;
+  }
+  .sig-info-td {
+    vertical-align: middle;
+    padding-left: 16pt;
+    font-size: 10pt;
+    line-height: 1.35;
+    color: #4a5568;
+  }
+  .sig-thanks {
+    font-size: 10.5pt;
+    color: #2d3748;
+    margin-bottom: 2px;
+  }
+  .sig-name {
+    font-size: 11pt;
+    font-weight: 700;
+    color: #0f2c59;
+  }
+  .sig-desig {
+    font-size: 9.5pt;
+    color: #4a5568;
+    margin-bottom: 3px;
+  }
+  .sig-company {
+    font-size: 10pt;
+    font-weight: 700;
+    color: #2d3748;
+  }
+  .sig-contact {
+    font-size: 9pt;
+    color: #4a5568;
+    margin-top: 3px;
+  }
+  .sig-link {
+    color: #0f2c59;
+    text-decoration: underline;
+    font-weight: 600;
+  }
+  .footer-bar {
+    background-color: #f8fafc;
+    border-top: 1px solid #e2e8f0;
+    padding: 14pt 24pt;
+    text-align: center;
+    font-size: 9.5pt;
+    color: #718096;
+    line-height: 1.4;
+  }
+&lt;/style&gt;
+&lt;/head&gt;
+&lt;body&gt;
+  &lt;div class="email-container"&gt;
+    &lt;div class="email-body"&gt;
+      &lt;p&gt;Dear Raghav Tiwari,&lt;/p&gt;
+      &lt;p&gt;Greetings from &lt;strong&gt;SAPCON Instruments Pvt. Ltd.&lt;/strong&gt;&lt;/p&gt;
+      &lt;p style="margin-top:12pt;"&gt;Please find attached our product details featuring the &lt;a href="https://www.sapconinstruments.com/products/vibrating-fork-level-switch-elixir" target="_blank" style="color:#0f2c59; font-weight:700; text-decoration:underline;"&gt;Vibrating Fork Level Switch (Elixir)&lt;/a&gt; for Liquid Point Level Detection in Storage Silos.&lt;/p&gt;
+      &lt;p style="margin:12pt 0; line-height:1.5; color:#2d3748;"&gt;Thank you for reaching out regarding our Elixir level switch for your liquid silo requirement. The Elixir is well-suited for liquid point level switching as its tuning fork design has no moving parts and operates reliably without requiring calibration across varying liquid densities. Could you please share the liquid media type, operating temperature, and process connection size so I can send over the exact GA drawing and wiring diagram?&lt;/p&gt;
+      &lt;p style="margin-top:12pt;"&gt;We would be pleased to support your project and regular instrumentation requirements and provide further technical or commercial details based on your application.&lt;/p&gt;
+      &lt;p style="margin-top:12pt; margin-bottom:0;"&gt;Looking forward to your requirements.&lt;/p&gt;
+    &lt;/div&gt;
+    &lt;div class="product-image-wrap" style="background-color:#ffffff; padding:12pt 20pt 16pt 20pt; text-align:center;"&gt;
+      &lt;a href="https://www.sapconinstruments.com/products/vibrating-fork-level-switch-elixir" target="_blank"&gt;
+        &lt;img src="/images/image2.png" alt="Vibrating Fork Level Switch (Elixir)" style="max-width:520px; width:100%; height:auto; border-radius:6px; border:1px solid #edf2f7; display:inline-block;"&gt;
+      &lt;/a&gt;
+    &lt;/div&gt;
+    &lt;div class="signature-card"&gt;
+      &lt;table class="sig-table"&gt;
+        &lt;tr&gt;
+          &lt;td class="sig-logo-td"&gt;
+            &lt;img src="/images/image1.png" alt="SAPCON Instruments Official Logo"&gt;
+          &lt;/td&gt;
+          &lt;td class="sig-info-td"&gt;
+            &lt;div class="sig-thanks"&gt;Thanks &amp;amp; Regards,&lt;/div&gt;
+            &lt;div class="sig-name"&gt;Elvis Joseph&lt;/div&gt;
+            &lt;div class="sig-desig"&gt;Regional Manager – South India Sales&lt;/div&gt;
+            &lt;div class="sig-company"&gt;SAPCON Instruments Pvt. Ltd.&lt;/div&gt;
+            &lt;div class="sig-contact"&gt;
+              P: 8871428228 / 0731-4757576, 75&lt;br&gt;
+              W: &lt;a href="https://www.sapconinstruments.com" class="sig-link" target="_blank"&gt;sapconinstruments.com&lt;/a&gt;
+            &lt;/div&gt;
+          &lt;/td&gt;
+        &lt;/tr&gt;
+      &lt;/table&gt;
+    &lt;/div&gt;
+    &lt;div class="footer-bar"&gt;
+      &lt;div&gt;&amp;copy; 2026 SAPCON Instruments. All rights reserved.&lt;/div&gt;
+      &lt;div&gt;Process Control Instrumentation &amp;bull; Indore, India&lt;/div&gt;
+    &lt;/div&gt;
+  &lt;/div&gt;
+&lt;/body&gt;
+&lt;/html&gt;</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Waiting for Approval</v>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21" xml:space="preserve">
+      <c r="A21" t="str">
+        <v>IMA</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Rahaber Raza</v>
+      </c>
+      <c r="C21" t="str">
+        <v>ramsharma9724@gmail.com</v>
+      </c>
+      <c r="D21" t="str">
+        <v>we need vital and elixer and RF admistance for my plant urgent basis</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Urgent level switch requirement for IMA plant</v>
+      </c>
+      <c r="F21" t="str" xml:space="preserve">
+        <v xml:space="preserve">&lt;!DOCTYPE html&gt;
+&lt;html lang="en"&gt;
+&lt;head&gt;
+&lt;meta charset="UTF-8"&gt;
+&lt;meta name="viewport" content="width=device-width, initial-scale=1.0"&gt;
+&lt;title&gt;SAPCON Instruments&lt;/title&gt;
+&lt;style type="text/css"&gt;
+  body {
+    margin: 0;
+    padding: 20px 0;
+    background-color: #f1f5f9;
+    font-family: Arial, Helvetica, sans-serif;
+    color: #2d3748;
+    -webkit-font-smoothing: antialiased;
+  }
+  .email-container {
+    max-width: 620px;
+    margin: 0 auto;
+    background-color: #ffffff;
+    border: 1px solid #e2e8f0;
+    border-radius: 8px;
+    overflow: hidden;
+    box-shadow: 0 4px 16px rgba(15, 44, 89, 0.08);
+  }
+  .email-body {
+    padding: 24pt 24pt 14pt 24pt;
+    font-size: 11pt;
+    line-height: 1.5;
+    color: #2d3748;
+  }
+  .email-body p {
+    margin: 0 0 10pt 0;
+  }
+  .signature-card {
+    background-color: #ffffff;
+    border-top: 1px solid #e2e8f0;
+    padding: 16pt 24pt;
+  }
+  .sig-table {
+    width: 100%;
+    border-collapse: collapse;
+  }
+  .sig-logo-td {
+    width: 95px;
+    vertical-align: middle;
+    padding-right: 16pt;
+    border-right: 1.5pt solid #0f2c59;
+  }
+  .sig-logo-td img {
+    width: 88px;
+    height: auto;
+    display: block;
+  }
+  .sig-info-td {
+    vertical-align: middle;
+    padding-left: 16pt;
+    font-size: 10pt;
+    line-height: 1.35;
+    color: #4a5568;
+  }
+  .sig-thanks {
+    font-size: 10.5pt;
+    color: #2d3748;
+    margin-bottom: 2px;
+  }
+  .sig-name {
+    font-size: 11pt;
+    font-weight: 700;
+    color: #0f2c59;
+  }
+  .sig-desig {
+    font-size: 9.5pt;
+    color: #4a5568;
+    margin-bottom: 3px;
+  }
+  .sig-company {
+    font-size: 10pt;
+    font-weight: 700;
+    color: #2d3748;
+  }
+  .sig-contact {
+    font-size: 9pt;
+    color: #4a5568;
+    margin-top: 3px;
+  }
+  .sig-link {
+    color: #0f2c59;
+    text-decoration: underline;
+    font-weight: 600;
+  }
+  .footer-bar {
+    background-color: #f8fafc;
+    border-top: 1px solid #e2e8f0;
+    padding: 14pt 24pt;
+    text-align: center;
+    font-size: 9.5pt;
+    color: #718096;
+    line-height: 1.4;
+  }
+&lt;/style&gt;
+&lt;/head&gt;
+&lt;body&gt;
+  &lt;div class="email-container"&gt;
+    &lt;div class="email-body"&gt;
+      &lt;p&gt;Dear Rahaber Raza,&lt;/p&gt;
+      &lt;p&gt;Greetings from &lt;strong&gt;SAPCON Instruments Pvt. Ltd.&lt;/strong&gt;&lt;/p&gt;
+      &lt;p style="margin-top:12pt;"&gt;Please find attached our product details featuring the &lt;a href="https://www.sapconinstruments.com/products/rf-admittance-level-switch-sla" target="_blank" style="color:#0f2c59; font-weight:700; text-decoration:underline;"&gt;RF Admittance Level Switch (SLA)&lt;/a&gt; for Point Level Detection with Coating &amp; Buildup Immunity.&lt;/p&gt;
+      &lt;p style="margin:12pt 0; line-height:1.5; color:#2d3748;"&gt;Thank you for getting in touch regarding your urgent requirement for our RF Admittance and Elixir switches at IMA. Our SLA series utilizes driven-shield coat-guard circuitry to prevent false switching from sticky material buildup on the probe, ensuring maintenance-free point level control. Please share your process media, vessel operating temperatures, and mounting nozzle sizes so we can finalize the dimensional drawings and line up fast-track dispatch for you.&lt;/p&gt;
+      &lt;p style="margin-top:12pt;"&gt;We would be pleased to support your project and regular instrumentation requirements and provide further technical or commercial details based on your application.&lt;/p&gt;
+      &lt;p style="margin-top:12pt; margin-bottom:0;"&gt;Looking forward to your requirements.&lt;/p&gt;
+    &lt;/div&gt;
+    &lt;div class="product-image-wrap" style="background-color:#ffffff; padding:12pt 20pt 16pt 20pt; text-align:center;"&gt;
+      &lt;a href="https://www.sapconinstruments.com/products/rf-admittance-level-switch-sla" target="_blank"&gt;
+        &lt;img src="/images/image2.png" alt="RF Admittance Level Switch (SLA)" style="max-width:520px; width:100%; height:auto; border-radius:6px; border:1px solid #edf2f7; display:inline-block;"&gt;
+      &lt;/a&gt;
+    &lt;/div&gt;
+    &lt;div class="signature-card"&gt;
+      &lt;table class="sig-table"&gt;
+        &lt;tr&gt;
+          &lt;td class="sig-logo-td"&gt;
+            &lt;img src="/images/image1.png" alt="SAPCON Instruments Official Logo"&gt;
+          &lt;/td&gt;
+          &lt;td class="sig-info-td"&gt;
+            &lt;div class="sig-thanks"&gt;Thanks &amp;amp; Regards,&lt;/div&gt;
+            &lt;div class="sig-name"&gt;Elvis Joseph&lt;/div&gt;
+            &lt;div class="sig-desig"&gt;Regional Manager – South India Sales&lt;/div&gt;
+            &lt;div class="sig-company"&gt;SAPCON Instruments Pvt. Ltd.&lt;/div&gt;
+            &lt;div class="sig-contact"&gt;
+              P: 8871428228 / 0731-4757576, 75&lt;br&gt;
+              W: &lt;a href="https://www.sapconinstruments.com" class="sig-link" target="_blank"&gt;sapconinstruments.com&lt;/a&gt;
+            &lt;/div&gt;
+          &lt;/td&gt;
+        &lt;/tr&gt;
+      &lt;/table&gt;
+    &lt;/div&gt;
+    &lt;div class="footer-bar"&gt;
+      &lt;div&gt;&amp;copy; 2026 SAPCON Instruments. All rights reserved.&lt;/div&gt;
+      &lt;div&gt;Process Control Instrumentation &amp;bull; Indore, India&lt;/div&gt;
+    &lt;/div&gt;
+  &lt;/div&gt;
+&lt;/body&gt;
+&lt;/html&gt;</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Waiting for Approval</v>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22" xml:space="preserve">
+      <c r="A22" t="str">
+        <v>Nextzee</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Raghav Tiwari</v>
+      </c>
+      <c r="C22" t="str">
+        <v>rt191708@gmail.com</v>
+      </c>
+      <c r="D22" t="str">
+        <v>we need elixer for silo liquid nature</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Technical details: Elixir level switch for Nextzee liquid silo</v>
+      </c>
+      <c r="F22" t="str" xml:space="preserve">
+        <v xml:space="preserve">&lt;!DOCTYPE html&gt;
+&lt;html lang="en"&gt;
+&lt;head&gt;
+&lt;meta charset="UTF-8"&gt;
+&lt;meta name="viewport" content="width=device-width, initial-scale=1.0"&gt;
+&lt;title&gt;SAPCON Instruments&lt;/title&gt;
+&lt;style type="text/css"&gt;
+  body {
+    margin: 0;
+    padding: 20px 0;
+    background-color: #f1f5f9;
+    font-family: Arial, Helvetica, sans-serif;
+    color: #2d3748;
+    -webkit-font-smoothing: antialiased;
+  }
+  .email-container {
+    max-width: 620px;
+    margin: 0 auto;
+    background-color: #ffffff;
+    border: 1px solid #e2e8f0;
+    border-radius: 8px;
+    overflow: hidden;
+    box-shadow: 0 4px 16px rgba(15, 44, 89, 0.08);
+  }
+  .email-body {
+    padding: 24pt 24pt 14pt 24pt;
+    font-size: 11pt;
+    line-height: 1.5;
+    color: #2d3748;
+  }
+  .email-body p {
+    margin: 0 0 10pt 0;
+  }
+  .signature-card {
+    background-color: #ffffff;
+    border-top: 1px solid #e2e8f0;
+    padding: 16pt 24pt;
+  }
+  .sig-table {
+    width: 100%;
+    border-collapse: collapse;
+  }
+  .sig-logo-td {
+    width: 95px;
+    vertical-align: middle;
+    padding-right: 16pt;
+    border-right: 1.5pt solid #0f2c59;
+  }
+  .sig-logo-td img {
+    width: 88px;
+    height: auto;
+    display: block;
+  }
+  .sig-info-td {
+    vertical-align: middle;
+    padding-left: 16pt;
+    font-size: 10pt;
+    line-height: 1.35;
+    color: #4a5568;
+  }
+  .sig-thanks {
+    font-size: 10.5pt;
+    color: #2d3748;
+    margin-bottom: 2px;
+  }
+  .sig-name {
+    font-size: 11pt;
+    font-weight: 700;
+    color: #0f2c59;
+  }
+  .sig-desig {
+    font-size: 9.5pt;
+    color: #4a5568;
+    margin-bottom: 3px;
+  }
+  .sig-company {
+    font-size: 10pt;
+    font-weight: 700;
+    color: #2d3748;
+  }
+  .sig-contact {
+    font-size: 9pt;
+    color: #4a5568;
+    margin-top: 3px;
+  }
+  .sig-link {
+    color: #0f2c59;
+    text-decoration: underline;
+    font-weight: 600;
+  }
+  .footer-bar {
+    background-color: #f8fafc;
+    border-top: 1px solid #e2e8f0;
+    padding: 14pt 24pt;
+    text-align: center;
+    font-size: 9.5pt;
+    color: #718096;
+    line-height: 1.4;
+  }
+&lt;/style&gt;
+&lt;/head&gt;
+&lt;body&gt;
+  &lt;div class="email-container"&gt;
+    &lt;div class="email-body"&gt;
+      &lt;p&gt;Dear Raghav Tiwari,&lt;/p&gt;
+      &lt;p&gt;Greetings from &lt;strong&gt;SAPCON Instruments Pvt. Ltd.&lt;/strong&gt;&lt;/p&gt;
+      &lt;p style="margin-top:12pt;"&gt;Please find attached our product details featuring the &lt;a href="https://www.sapconinstruments.com/products/vibrating-fork-level-switch-elixir" target="_blank" style="color:#0f2c59; font-weight:700; text-decoration:underline;"&gt;Vibrating Fork Level Switch (Elixir)&lt;/a&gt; for Point Level Detection in Liquid Silos &amp; Process Tanks.&lt;/p&gt;
+      &lt;p style="margin:12pt 0; line-height:1.5; color:#2d3748;"&gt;Thank you for reaching out regarding our Elixir vibrating fork switch for your liquid silo. It provides reliable high or low-level switching independent of flow, turbulence, or dielectric changes, with no moving parts to wear out. Could you share your process connection preference (threaded or flanged) and required insertion length so I can send over the exact GA drawing and wiring diagram?&lt;/p&gt;
+      &lt;p style="margin-top:12pt;"&gt;We would be pleased to support your project and regular instrumentation requirements and provide further technical or commercial details based on your application.&lt;/p&gt;
+      &lt;p style="margin-top:12pt; margin-bottom:0;"&gt;Looking forward to your requirements.&lt;/p&gt;
+    &lt;/div&gt;
+    &lt;div class="product-image-wrap" style="background-color:#ffffff; padding:12pt 20pt 16pt 20pt; text-align:center;"&gt;
+      &lt;a href="https://www.sapconinstruments.com/products/vibrating-fork-level-switch-elixir" target="_blank"&gt;
+        &lt;img src="/images/image2.png" alt="Vibrating Fork Level Switch (Elixir)" style="max-width:520px; width:100%; height:auto; border-radius:6px; border:1px solid #edf2f7; display:inline-block;"&gt;
+      &lt;/a&gt;
+    &lt;/div&gt;
+    &lt;div class="signature-card"&gt;
+      &lt;table class="sig-table"&gt;
+        &lt;tr&gt;
+          &lt;td class="sig-logo-td"&gt;
+            &lt;img src="/images/image1.png" alt="SAPCON Instruments Official Logo"&gt;
+          &lt;/td&gt;
+          &lt;td class="sig-info-td"&gt;
+            &lt;div class="sig-thanks"&gt;Thanks &amp;amp; Regards,&lt;/div&gt;
+            &lt;div class="sig-name"&gt;Elvis Joseph&lt;/div&gt;
+            &lt;div class="sig-desig"&gt;Regional Manager – South India Sales&lt;/div&gt;
+            &lt;div class="sig-company"&gt;SAPCON Instruments Pvt. Ltd.&lt;/div&gt;
+            &lt;div class="sig-contact"&gt;
+              P: 8871428228 / 0731-4757576, 75&lt;br&gt;
+              W: &lt;a href="https://www.sapconinstruments.com" class="sig-link" target="_blank"&gt;sapconinstruments.com&lt;/a&gt;
+            &lt;/div&gt;
+          &lt;/td&gt;
+        &lt;/tr&gt;
+      &lt;/table&gt;
+    &lt;/div&gt;
+    &lt;div class="footer-bar"&gt;
+      &lt;div&gt;&amp;copy; 2026 SAPCON Instruments. All rights reserved.&lt;/div&gt;
+      &lt;div&gt;Process Control Instrumentation &amp;bull; Indore, India&lt;/div&gt;
+    &lt;/div&gt;
+  &lt;/div&gt;
+&lt;/body&gt;
+&lt;/html&gt;</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="H22" t="str">
+        <v>17 Oct 2026, 10:59 am</v>
+      </c>
+    </row>
+    <row r="23" xml:space="preserve">
+      <c r="A23" t="str">
+        <v>IMA</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Rahaber Raza</v>
+      </c>
+      <c r="C23" t="str">
+        <v>ramsharma9724@gmail.com</v>
+      </c>
+      <c r="D23" t="str">
+        <v>we need vital and elixer and RF admistance for my plant urgent basis</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Urgent level switch requirement (RF Admittance, Elixir &amp; Vital) for IMA</v>
+      </c>
+      <c r="F23" t="str" xml:space="preserve">
+        <v xml:space="preserve">&lt;!DOCTYPE html&gt;
+&lt;html lang="en"&gt;
+&lt;head&gt;
+&lt;meta charset="UTF-8"&gt;
+&lt;meta name="viewport" content="width=device-width, initial-scale=1.0"&gt;
+&lt;title&gt;SAPCON Instruments&lt;/title&gt;
+&lt;style type="text/css"&gt;
+  body {
+    margin: 0;
+    padding: 20px 0;
+    background-color: #f1f5f9;
+    font-family: Arial, Helvetica, sans-serif;
+    color: #2d3748;
+    -webkit-font-smoothing: antialiased;
+  }
+  .email-container {
+    max-width: 620px;
+    margin: 0 auto;
+    background-color: #ffffff;
+    border: 1px solid #e2e8f0;
+    border-radius: 8px;
+    overflow: hidden;
+    box-shadow: 0 4px 16px rgba(15, 44, 89, 0.08);
+  }
+  .email-body {
+    padding: 24pt 24pt 14pt 24pt;
+    font-size: 11pt;
+    line-height: 1.5;
+    color: #2d3748;
+  }
+  .email-body p {
+    margin: 0 0 10pt 0;
+  }
+  .signature-card {
+    background-color: #ffffff;
+    border-top: 1px solid #e2e8f0;
+    padding: 16pt 24pt;
+  }
+  .sig-table {
+    width: 100%;
+    border-collapse: collapse;
+  }
+  .sig-logo-td {
+    width: 95px;
+    vertical-align: middle;
+    padding-right: 16pt;
+    border-right: 1.5pt solid #0f2c59;
+  }
+  .sig-logo-td img {
+    width: 88px;
+    height: auto;
+    display: block;
+  }
+  .sig-info-td {
+    vertical-align: middle;
+    padding-left: 16pt;
+    font-size: 10pt;
+    line-height: 1.35;
+    color: #4a5568;
+  }
+  .sig-thanks {
+    font-size: 10.5pt;
+    color: #2d3748;
+    margin-bottom: 2px;
+  }
+  .sig-name {
+    font-size: 11pt;
+    font-weight: 700;
+    color: #0f2c59;
+  }
+  .sig-desig {
+    font-size: 9.5pt;
+    color: #4a5568;
+    margin-bottom: 3px;
+  }
+  .sig-company {
+    font-size: 10pt;
+    font-weight: 700;
+    color: #2d3748;
+  }
+  .sig-contact {
+    font-size: 9pt;
+    color: #4a5568;
+    margin-top: 3px;
+  }
+  .sig-link {
+    color: #0f2c59;
+    text-decoration: underline;
+    font-weight: 600;
+  }
+  .footer-bar {
+    background-color: #f8fafc;
+    border-top: 1px solid #e2e8f0;
+    padding: 14pt 24pt;
+    text-align: center;
+    font-size: 9.5pt;
+    color: #718096;
+    line-height: 1.4;
+  }
+&lt;/style&gt;
+&lt;/head&gt;
+&lt;body&gt;
+  &lt;div class="email-container"&gt;
+    &lt;div class="email-body"&gt;
+      &lt;p&gt;Dear Mr. Rahaber Raza,&lt;/p&gt;
+      &lt;p&gt;Greetings from &lt;strong&gt;SAPCON Instruments Pvt. Ltd.&lt;/strong&gt;&lt;/p&gt;
+      &lt;p style="margin-top:12pt;"&gt;Please find attached our product details featuring the &lt;a href="https://www.sapconinstruments.com/products/rf-admittance-level-switch-sla" target="_blank" style="color:#0f2c59; font-weight:700; text-decoration:underline;"&gt;RF Admittance Level Switch (SLA)&lt;/a&gt; for Point Level Detection with Coating Immunity.&lt;/p&gt;
+      &lt;p style="margin:12pt 0; line-height:1.5; color:#2d3748;"&gt;Thank you for reaching out regarding your urgent plant requirement for the Vital, Elixir, and RF Admittance switches. We manufacture all three series at our Indore facility, with our RF Admittance (SLA) units specifically featuring active-shield circuitry to eliminate false switching from material buildup and probe coating. Since your timeline is tight, please share your mounting connection sizes, operating temperature, and probe lengths so I can dispatch the GA drawings and offer today.&lt;/p&gt;
+      &lt;p style="margin-top:12pt;"&gt;We would be pleased to support your project and regular instrumentation requirements and provide further technical or commercial details based on your application.&lt;/p&gt;
+      &lt;p style="margin-top:12pt; margin-bottom:0;"&gt;Looking forward to your requirements.&lt;/p&gt;
+    &lt;/div&gt;
+    &lt;div class="product-image-wrap" style="background-color:#ffffff; padding:12pt 20pt 16pt 20pt; text-align:center;"&gt;
+      &lt;a href="https://www.sapconinstruments.com/products/rf-admittance-level-switch-sla" target="_blank"&gt;
+        &lt;img src="/images/image2.png" alt="RF Admittance Level Switch (SLA)" style="max-width:520px; width:100%; height:auto; border-radius:6px; border:1px solid #edf2f7; display:inline-block;"&gt;
+      &lt;/a&gt;
+    &lt;/div&gt;
+    &lt;div class="signature-card"&gt;
+      &lt;table class="sig-table"&gt;
+        &lt;tr&gt;
+          &lt;td class="sig-logo-td"&gt;
+            &lt;img src="/images/image1.png" alt="SAPCON Instruments Official Logo"&gt;
+          &lt;/td&gt;
+          &lt;td class="sig-info-td"&gt;
+            &lt;div class="sig-thanks"&gt;Thanks &amp;amp; Regards,&lt;/div&gt;
+            &lt;div class="sig-name"&gt;Elvis Joseph&lt;/div&gt;
+            &lt;div class="sig-desig"&gt;Regional Manager – South India Sales&lt;/div&gt;
+            &lt;div class="sig-company"&gt;SAPCON Instruments Pvt. Ltd.&lt;/div&gt;
+            &lt;div class="sig-contact"&gt;
+              P: 8871428228 / 0731-4757576, 75&lt;br&gt;
+              W: &lt;a href="https://www.sapconinstruments.com" class="sig-link" target="_blank"&gt;sapconinstruments.com&lt;/a&gt;
+            &lt;/div&gt;
+          &lt;/td&gt;
+        &lt;/tr&gt;
+      &lt;/table&gt;
+    &lt;/div&gt;
+    &lt;div class="footer-bar"&gt;
+      &lt;div&gt;&amp;copy; 2026 SAPCON Instruments. All rights reserved.&lt;/div&gt;
+      &lt;div&gt;Process Control Instrumentation &amp;bull; Indore, India&lt;/div&gt;
+    &lt;/div&gt;
+  &lt;/div&gt;
+&lt;/body&gt;
+&lt;/html&gt;</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="H23" t="str">
+        <v>17 Oct 2026, 11:00 am</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H23"/>
+  </ignoredErrors>
 </worksheet>
 </file>